--- a/downloads/WC2026-GROUPS-BONUS.xlsx
+++ b/downloads/WC2026-GROUPS-BONUS.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bob\Desktop\wc2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF8D750-861F-4BF9-9630-75D1BB3C24A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CB0336-0C42-456E-B0DC-0297AACE4AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="HiDxC2zhGT3wfx+5QZRw1x4pNxpSD7Thht9s43AhnOgV4JR+pqxyoVxeHHDhNa0gG0EVs2c6Wd+T4D4bjRr3Ag==" workbookSaltValue="PrnP9sc2NIUodcWwYN2RWg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{74C112C2-5EB1-4FE2-B062-25000C577A87}"/>
   </bookViews>
@@ -16,9 +17,6 @@
     <sheet name="Group Stage" sheetId="1" r:id="rId1"/>
     <sheet name="Lucky Bonus" sheetId="2" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <definedNames>
     <definedName name="A_Team1">'Group Stage'!$C$58</definedName>
     <definedName name="A_Team2">'Group Stage'!$C$59</definedName>
@@ -542,9 +540,6 @@
     <t>France vs Senegal</t>
   </si>
   <si>
-    <t>Bolivia vs Norway</t>
-  </si>
-  <si>
     <t>Argentina vs Algeria</t>
   </si>
   <si>
@@ -605,9 +600,6 @@
     <t>Argentina vs Austria</t>
   </si>
   <si>
-    <t>France vs Bolivia</t>
-  </si>
-  <si>
     <t>Norway vs Senegal</t>
   </si>
   <si>
@@ -654,9 +646,6 @@
   </si>
   <si>
     <t>Norway vs France</t>
-  </si>
-  <si>
-    <t>Senegal vs Bolivia</t>
   </si>
   <si>
     <t>Cabo Verde vs Saudi Arabia</t>
@@ -752,6 +741,15 @@
       </rPr>
       <t>:</t>
     </r>
+  </si>
+  <si>
+    <t>Iraq vs Norway</t>
+  </si>
+  <si>
+    <t>France vs Iraq</t>
+  </si>
+  <si>
+    <t>Senegal vs Iraq</t>
   </si>
 </sst>
 </file>
@@ -1611,6 +1609,24 @@
     <xf numFmtId="0" fontId="14" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -1634,24 +1650,6 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2228,264 +2226,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Group Stage"/>
-      <sheetName val="GroupA"/>
-      <sheetName val="GroupB"/>
-      <sheetName val="GroupC"/>
-      <sheetName val="GroupD"/>
-      <sheetName val="GroupE"/>
-      <sheetName val="GroupF"/>
-      <sheetName val="GroupG"/>
-      <sheetName val="GroupH"/>
-      <sheetName val="GroupI"/>
-      <sheetName val="GroupJ"/>
-      <sheetName val="GroupK"/>
-      <sheetName val="GroupL"/>
-      <sheetName val="Lucky Bonus"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="6">
-          <cell r="AG6">
-            <v>10</v>
-          </cell>
-          <cell r="AJ6">
-            <v>0</v>
-          </cell>
-          <cell r="AN6">
-            <v>0</v>
-          </cell>
-          <cell r="AT6">
-            <v>0</v>
-          </cell>
-          <cell r="AU6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2">
-        <row r="6">
-          <cell r="AG6">
-            <v>10</v>
-          </cell>
-          <cell r="AJ6">
-            <v>0</v>
-          </cell>
-          <cell r="AN6">
-            <v>0</v>
-          </cell>
-          <cell r="AT6">
-            <v>0</v>
-          </cell>
-          <cell r="AU6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3">
-        <row r="6">
-          <cell r="AG6">
-            <v>8</v>
-          </cell>
-          <cell r="AJ6">
-            <v>24</v>
-          </cell>
-          <cell r="AN6">
-            <v>0</v>
-          </cell>
-          <cell r="AT6">
-            <v>0</v>
-          </cell>
-          <cell r="AU6">
-            <v>10</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4">
-        <row r="6">
-          <cell r="AG6">
-            <v>8</v>
-          </cell>
-          <cell r="AJ6">
-            <v>24</v>
-          </cell>
-          <cell r="AN6">
-            <v>0</v>
-          </cell>
-          <cell r="AT6">
-            <v>0</v>
-          </cell>
-          <cell r="AU6">
-            <v>10</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5">
-        <row r="6">
-          <cell r="AG6">
-            <v>9</v>
-          </cell>
-          <cell r="AJ6">
-            <v>16</v>
-          </cell>
-          <cell r="AN6">
-            <v>0</v>
-          </cell>
-          <cell r="AT6">
-            <v>0</v>
-          </cell>
-          <cell r="AU6">
-            <v>10</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6">
-        <row r="6">
-          <cell r="AG6">
-            <v>8</v>
-          </cell>
-          <cell r="AJ6">
-            <v>24</v>
-          </cell>
-          <cell r="AN6">
-            <v>0</v>
-          </cell>
-          <cell r="AT6">
-            <v>0</v>
-          </cell>
-          <cell r="AU6">
-            <v>10</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="7">
-        <row r="6">
-          <cell r="AG6">
-            <v>8</v>
-          </cell>
-          <cell r="AJ6">
-            <v>24</v>
-          </cell>
-          <cell r="AN6">
-            <v>0</v>
-          </cell>
-          <cell r="AT6">
-            <v>0</v>
-          </cell>
-          <cell r="AU6">
-            <v>10</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="8">
-        <row r="6">
-          <cell r="AG6">
-            <v>10</v>
-          </cell>
-          <cell r="AJ6">
-            <v>0</v>
-          </cell>
-          <cell r="AN6">
-            <v>0</v>
-          </cell>
-          <cell r="AT6">
-            <v>0</v>
-          </cell>
-          <cell r="AU6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="9">
-        <row r="6">
-          <cell r="AG6">
-            <v>10</v>
-          </cell>
-          <cell r="AJ6">
-            <v>0</v>
-          </cell>
-          <cell r="AN6">
-            <v>0</v>
-          </cell>
-          <cell r="AT6">
-            <v>0</v>
-          </cell>
-          <cell r="AU6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="10">
-        <row r="6">
-          <cell r="AG6">
-            <v>8</v>
-          </cell>
-          <cell r="AJ6">
-            <v>24</v>
-          </cell>
-          <cell r="AN6">
-            <v>0</v>
-          </cell>
-          <cell r="AT6">
-            <v>0</v>
-          </cell>
-          <cell r="AU6">
-            <v>10</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="11">
-        <row r="6">
-          <cell r="AG6">
-            <v>9</v>
-          </cell>
-          <cell r="AJ6">
-            <v>24</v>
-          </cell>
-          <cell r="AN6">
-            <v>0</v>
-          </cell>
-          <cell r="AT6">
-            <v>0</v>
-          </cell>
-          <cell r="AU6">
-            <v>10</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="12">
-        <row r="6">
-          <cell r="AG6">
-            <v>10</v>
-          </cell>
-          <cell r="AJ6">
-            <v>0</v>
-          </cell>
-          <cell r="AN6">
-            <v>0</v>
-          </cell>
-          <cell r="AT6">
-            <v>0</v>
-          </cell>
-          <cell r="AU6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="13" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2839,14 +2579,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="str">
-        <f>IF(OR(AND(J4=3,J5=3,J6=3,J7=3),AND(B1="ties",K3="GROUP COMPLETE")),"TIES","OK")</f>
-        <v>OK</v>
-      </c>
-      <c r="B1" s="2" t="str">
-        <f>IF([1]GroupA!$AG$6=10,"",IF(AND([1]GroupA!$AN$6&lt;&gt;24,[1]GroupA!$AJ$6&lt;&gt;24,[1]GroupA!$AG$6&lt;&gt;24,OR([1]GroupA!$AT$6=10,[1]GroupA!$AU$6=10)),"ties","group good"))</f>
-        <v/>
-      </c>
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
@@ -2857,30 +2591,24 @@
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="4"/>
-      <c r="M1" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
+      <c r="M1" s="83" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
       <c r="R1" s="5"/>
       <c r="S1" s="6"/>
-      <c r="T1" s="78" t="s">
+      <c r="T1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="U1" s="78"/>
-      <c r="V1" s="78"/>
-      <c r="W1" s="78"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="1" t="str">
-        <f>IF(OR(AND(AH4=3,AH5=3,AH6=3,AH7=3),AND(Z1="ties",AI3="GROUP COMPLETE")),"TIES","OK")</f>
-        <v>OK</v>
-      </c>
-      <c r="Z1" s="2" t="str">
-        <f>IF([1]GroupB!$AG$6=10,"",IF(AND([1]GroupB!$AN$6&lt;&gt;24,[1]GroupB!$AJ$6&lt;&gt;24,[1]GroupB!$AG$6&lt;&gt;24,OR([1]GroupB!$AT$6=10,[1]GroupB!$AU$6=10)),"ties","group good"))</f>
-        <v/>
-      </c>
+      <c r="U1" s="83"/>
+      <c r="V1" s="83"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="2"/>
       <c r="AA1" s="3"/>
       <c r="AB1" s="3"/>
       <c r="AC1" s="3"/>
@@ -2895,16 +2623,16 @@
     <row r="2" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
       <c r="K2" s="8"/>
       <c r="L2" s="9"/>
       <c r="M2" s="10"/>
@@ -2921,16 +2649,16 @@
       <c r="X2" s="16"/>
       <c r="Y2" s="7"/>
       <c r="Z2" s="8"/>
-      <c r="AA2" s="80" t="s">
+      <c r="AA2" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="AB2" s="80"/>
-      <c r="AC2" s="80"/>
-      <c r="AD2" s="80"/>
-      <c r="AE2" s="80"/>
-      <c r="AF2" s="80"/>
-      <c r="AG2" s="80"/>
-      <c r="AH2" s="80"/>
+      <c r="AB2" s="85"/>
+      <c r="AC2" s="85"/>
+      <c r="AD2" s="85"/>
+      <c r="AE2" s="85"/>
+      <c r="AF2" s="85"/>
+      <c r="AG2" s="85"/>
+      <c r="AH2" s="85"/>
       <c r="AI2" s="8"/>
       <c r="AJ2" s="9"/>
     </row>
@@ -3027,11 +2755,11 @@
       <c r="AJ3" s="9"/>
     </row>
     <row r="4" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="str">
+      <c r="A4" s="82" t="str">
         <f>IF(K3="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="B4" s="77"/>
+      <c r="B4" s="82"/>
       <c r="C4" s="33" t="str" cm="1">
         <f t="array" ref="C4:J7">_xlfn._xlws.SORT(C58:J61,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Mexico</v>
@@ -3087,11 +2815,11 @@
         <f>B_Team4</f>
         <v>Switzerland</v>
       </c>
-      <c r="Y4" s="77" t="str">
+      <c r="Y4" s="82" t="str">
         <f>IF(AI3="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="Z4" s="77"/>
+      <c r="Z4" s="82"/>
       <c r="AA4" s="37" t="str" cm="1">
         <f t="array" ref="AA4:AH7">_xlfn._xlws.SORT(AA58:AH61,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Canada</v>
@@ -3121,11 +2849,11 @@
       <c r="AJ4" s="9"/>
     </row>
     <row r="5" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="77" t="str">
+      <c r="A5" s="82" t="str">
         <f>IF(K3="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="B5" s="77"/>
+      <c r="B5" s="82"/>
       <c r="C5" s="33" t="str">
         <v>South Africa</v>
       </c>
@@ -3180,11 +2908,11 @@
         <f>B_Team2</f>
         <v>Bosnia</v>
       </c>
-      <c r="Y5" s="77" t="str">
+      <c r="Y5" s="82" t="str">
         <f>IF(AI3="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="Z5" s="77"/>
+      <c r="Z5" s="82"/>
       <c r="AA5" s="37" t="str">
         <v>Bosnia</v>
       </c>
@@ -3213,11 +2941,11 @@
       <c r="AJ5" s="9"/>
     </row>
     <row r="6" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="77" t="str">
+      <c r="A6" s="82" t="str">
         <f>IF(K3="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="B6" s="77"/>
+      <c r="B6" s="82"/>
       <c r="C6" s="33" t="str">
         <v>South Korea</v>
       </c>
@@ -3272,11 +3000,11 @@
         <f>B_Team3</f>
         <v>Qatar</v>
       </c>
-      <c r="Y6" s="77" t="str">
+      <c r="Y6" s="82" t="str">
         <f>IF(AI3="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="Z6" s="77"/>
+      <c r="Z6" s="82"/>
       <c r="AA6" s="37" t="str">
         <v>Qatar</v>
       </c>
@@ -3305,11 +3033,11 @@
       <c r="AJ6" s="9"/>
     </row>
     <row r="7" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="77" t="str">
+      <c r="A7" s="82" t="str">
         <f>IF(K3="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="B7" s="77"/>
+      <c r="B7" s="82"/>
       <c r="C7" s="42" t="str">
         <v>Czechia</v>
       </c>
@@ -3364,11 +3092,11 @@
         <f>B_Team1</f>
         <v>Canada</v>
       </c>
-      <c r="Y7" s="77" t="str">
+      <c r="Y7" s="82" t="str">
         <f>IF(AI3="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="Z7" s="77"/>
+      <c r="Z7" s="82"/>
       <c r="AA7" s="46" t="str">
         <v>Switzerland</v>
       </c>
@@ -3495,14 +3223,8 @@
       <c r="AJ9" s="52"/>
     </row>
     <row r="10" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="str">
-        <f>IF(OR(AND(J13=3,J14=3,J15=3,J16=3),AND(B10="ties",K12="GROUP COMPLETE")),"TIES","OK")</f>
-        <v>OK</v>
-      </c>
-      <c r="B10" s="2" t="str">
-        <f>IF([1]GroupC!$AG$6=10,"",IF(AND([1]GroupC!$AN$6&lt;&gt;24,[1]GroupC!$AJ$6&lt;&gt;24,[1]GroupC!$AG$6&lt;&gt;24,OR([1]GroupC!$AT$6=10,[1]GroupC!$AU$6=10)),"ties","group good"))</f>
-        <v>group good</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="2"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -3513,30 +3235,24 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="4"/>
-      <c r="M10" s="78" t="s">
+      <c r="M10" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="N10" s="78"/>
-      <c r="O10" s="78"/>
-      <c r="P10" s="78"/>
-      <c r="Q10" s="78"/>
+      <c r="N10" s="83"/>
+      <c r="O10" s="83"/>
+      <c r="P10" s="83"/>
+      <c r="Q10" s="83"/>
       <c r="R10" s="59"/>
       <c r="S10" s="14"/>
-      <c r="T10" s="79" t="s">
+      <c r="T10" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="U10" s="79"/>
-      <c r="V10" s="79"/>
-      <c r="W10" s="79"/>
-      <c r="X10" s="79"/>
-      <c r="Y10" s="1" t="str">
-        <f>IF(OR(AND(AH13=3,AH14=3,AH15=3,AH16=3),AND(Z10="ties",AI12="GROUP COMPLETE")),"TIES","OK")</f>
-        <v>OK</v>
-      </c>
-      <c r="Z10" s="2" t="str">
-        <f>IF([1]GroupD!$AG$6=10,"",IF(AND([1]GroupD!$AN$6&lt;&gt;24,[1]GroupD!$AJ$6&lt;&gt;24,[1]GroupD!$AG$6&lt;&gt;24,OR([1]GroupD!$AT$6=10,[1]GroupD!$AU$6=10)),"ties","group good"))</f>
-        <v>group good</v>
-      </c>
+      <c r="U10" s="84"/>
+      <c r="V10" s="84"/>
+      <c r="W10" s="84"/>
+      <c r="X10" s="84"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="2"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
@@ -3551,16 +3267,16 @@
     <row r="11" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="8"/>
-      <c r="C11" s="80" t="s">
+      <c r="C11" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="80"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="80"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="85"/>
       <c r="K11" s="8"/>
       <c r="L11" s="9"/>
       <c r="M11" s="60"/>
@@ -3577,16 +3293,16 @@
       <c r="X11" s="16"/>
       <c r="Y11" s="7"/>
       <c r="Z11" s="8"/>
-      <c r="AA11" s="80" t="s">
+      <c r="AA11" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="AB11" s="80"/>
-      <c r="AC11" s="80"/>
-      <c r="AD11" s="80"/>
-      <c r="AE11" s="80"/>
-      <c r="AF11" s="80"/>
-      <c r="AG11" s="80"/>
-      <c r="AH11" s="80"/>
+      <c r="AB11" s="85"/>
+      <c r="AC11" s="85"/>
+      <c r="AD11" s="85"/>
+      <c r="AE11" s="85"/>
+      <c r="AF11" s="85"/>
+      <c r="AG11" s="85"/>
+      <c r="AH11" s="85"/>
       <c r="AI11" s="8"/>
       <c r="AJ11" s="9"/>
     </row>
@@ -3683,11 +3399,11 @@
       <c r="AJ12" s="9"/>
     </row>
     <row r="13" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="77" t="str">
+      <c r="A13" s="82" t="str">
         <f>IF(K12="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="B13" s="77"/>
+      <c r="B13" s="82"/>
       <c r="C13" s="33" t="str" cm="1">
         <f t="array" ref="C13:J16">_xlfn._xlws.SORT(C65:J68,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Brazil</v>
@@ -3743,11 +3459,11 @@
         <f>D_Team4</f>
         <v>Turkey</v>
       </c>
-      <c r="Y13" s="77" t="str">
+      <c r="Y13" s="82" t="str">
         <f>IF(AI12="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="Z13" s="77"/>
+      <c r="Z13" s="82"/>
       <c r="AA13" s="37" t="str" cm="1">
         <f t="array" ref="AA13:AH16">_xlfn._xlws.SORT(AA65:AH68,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>USA</v>
@@ -3777,11 +3493,11 @@
       <c r="AJ13" s="9"/>
     </row>
     <row r="14" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="77" t="str">
+      <c r="A14" s="82" t="str">
         <f>IF(K12="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="B14" s="77"/>
+      <c r="B14" s="82"/>
       <c r="C14" s="33" t="str">
         <v>Morocco</v>
       </c>
@@ -3836,11 +3552,11 @@
         <f>D_Team2</f>
         <v>Paraguay</v>
       </c>
-      <c r="Y14" s="77" t="str">
+      <c r="Y14" s="82" t="str">
         <f>IF(AI12="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="Z14" s="77"/>
+      <c r="Z14" s="82"/>
       <c r="AA14" s="37" t="str">
         <v>Paraguay</v>
       </c>
@@ -3869,11 +3585,11 @@
       <c r="AJ14" s="9"/>
     </row>
     <row r="15" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="77" t="str">
+      <c r="A15" s="82" t="str">
         <f>IF(K12="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="B15" s="77"/>
+      <c r="B15" s="82"/>
       <c r="C15" s="33" t="str">
         <v>Haiti</v>
       </c>
@@ -3928,11 +3644,11 @@
         <f>D_Team3</f>
         <v>Australia</v>
       </c>
-      <c r="Y15" s="77" t="str">
+      <c r="Y15" s="82" t="str">
         <f>IF(AI12="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="Z15" s="77"/>
+      <c r="Z15" s="82"/>
       <c r="AA15" s="37" t="str">
         <v>Australia</v>
       </c>
@@ -3961,11 +3677,11 @@
       <c r="AJ15" s="9"/>
     </row>
     <row r="16" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="77" t="str">
+      <c r="A16" s="82" t="str">
         <f>IF(K12="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="B16" s="77"/>
+      <c r="B16" s="82"/>
       <c r="C16" s="42" t="str">
         <v>Scotland</v>
       </c>
@@ -4020,11 +3736,11 @@
         <f>D_Team1</f>
         <v>USA</v>
       </c>
-      <c r="Y16" s="77" t="str">
+      <c r="Y16" s="82" t="str">
         <f>IF(AI12="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="Z16" s="77"/>
+      <c r="Z16" s="82"/>
       <c r="AA16" s="46" t="str">
         <v>Turkey</v>
       </c>
@@ -4151,14 +3867,8 @@
       <c r="AJ18" s="52"/>
     </row>
     <row r="19" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="str">
-        <f>IF(OR(AND(J22=3,J23=3,J24=3,J25=3),AND(B19="ties",K21="GROUP COMPLETE")),"TIES","OK")</f>
-        <v>OK</v>
-      </c>
-      <c r="B19" s="2" t="str">
-        <f>IF([1]GroupE!$AG$6=10,"",IF(AND([1]GroupE!$AN$6&lt;&gt;24,[1]GroupE!$AJ$6&lt;&gt;24,[1]GroupE!$AG$6&lt;&gt;24,OR([1]GroupE!$AT$6=10,[1]GroupE!$AU$6=10)),"ties","group good"))</f>
-        <v>ties</v>
-      </c>
+      <c r="A19" s="1"/>
+      <c r="B19" s="2"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -4169,30 +3879,24 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="4"/>
-      <c r="M19" s="78" t="s">
+      <c r="M19" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="N19" s="78"/>
-      <c r="O19" s="78"/>
-      <c r="P19" s="78"/>
-      <c r="Q19" s="78"/>
+      <c r="N19" s="83"/>
+      <c r="O19" s="83"/>
+      <c r="P19" s="83"/>
+      <c r="Q19" s="83"/>
       <c r="R19" s="59"/>
       <c r="S19" s="14"/>
-      <c r="T19" s="79" t="s">
+      <c r="T19" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="U19" s="79"/>
-      <c r="V19" s="79"/>
-      <c r="W19" s="79"/>
-      <c r="X19" s="79"/>
-      <c r="Y19" s="1" t="str">
-        <f>IF(OR(AND(AH22=3,AH23=3,AH24=3,AH25=3),AND(Z19="ties",AI21="GROUP COMPLETE")),"TIES","OK")</f>
-        <v>OK</v>
-      </c>
-      <c r="Z19" s="2" t="str">
-        <f>IF([1]GroupF!$AG$6=10,"",IF(AND([1]GroupF!$AN$6&lt;&gt;24,[1]GroupF!$AJ$6&lt;&gt;24,[1]GroupF!$AG$6&lt;&gt;24,OR([1]GroupF!$AT$6=10,[1]GroupF!$AU$6=10)),"ties","group good"))</f>
-        <v>group good</v>
-      </c>
+      <c r="U19" s="84"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="2"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
@@ -4207,16 +3911,16 @@
     <row r="20" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="8"/>
-      <c r="C20" s="80" t="s">
+      <c r="C20" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="80"/>
-      <c r="G20" s="80"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="80"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="85"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="85"/>
       <c r="K20" s="8"/>
       <c r="L20" s="9"/>
       <c r="M20" s="60"/>
@@ -4233,16 +3937,16 @@
       <c r="X20" s="16"/>
       <c r="Y20" s="7"/>
       <c r="Z20" s="8"/>
-      <c r="AA20" s="80" t="s">
+      <c r="AA20" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="AB20" s="80"/>
-      <c r="AC20" s="80"/>
-      <c r="AD20" s="80"/>
-      <c r="AE20" s="80"/>
-      <c r="AF20" s="80"/>
-      <c r="AG20" s="80"/>
-      <c r="AH20" s="80"/>
+      <c r="AB20" s="85"/>
+      <c r="AC20" s="85"/>
+      <c r="AD20" s="85"/>
+      <c r="AE20" s="85"/>
+      <c r="AF20" s="85"/>
+      <c r="AG20" s="85"/>
+      <c r="AH20" s="85"/>
       <c r="AI20" s="8"/>
       <c r="AJ20" s="9"/>
     </row>
@@ -4339,11 +4043,11 @@
       <c r="AJ21" s="9"/>
     </row>
     <row r="22" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="77" t="str">
+      <c r="A22" s="82" t="str">
         <f>IF(K21="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="B22" s="77"/>
+      <c r="B22" s="82"/>
       <c r="C22" s="33" t="str" cm="1">
         <f t="array" ref="C22:J25">_xlfn._xlws.SORT(C72:J75,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Germany</v>
@@ -4399,11 +4103,11 @@
         <f>F_Team4</f>
         <v>Tunisia</v>
       </c>
-      <c r="Y22" s="77" t="str">
+      <c r="Y22" s="82" t="str">
         <f>IF(AI21="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="Z22" s="77"/>
+      <c r="Z22" s="82"/>
       <c r="AA22" s="37" t="str" cm="1">
         <f t="array" ref="AA22:AH25">_xlfn._xlws.SORT(AA72:AH75,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Netherlands</v>
@@ -4433,11 +4137,11 @@
       <c r="AJ22" s="9"/>
     </row>
     <row r="23" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="77" t="str">
+      <c r="A23" s="82" t="str">
         <f>IF(K21="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="B23" s="77"/>
+      <c r="B23" s="82"/>
       <c r="C23" s="37" t="str">
         <v>Curacao</v>
       </c>
@@ -4492,11 +4196,11 @@
         <f>F_Team3</f>
         <v>Sweden</v>
       </c>
-      <c r="Y23" s="77" t="str">
+      <c r="Y23" s="82" t="str">
         <f>IF(AI21="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="Z23" s="77"/>
+      <c r="Z23" s="82"/>
       <c r="AA23" s="37" t="str">
         <v>Japan</v>
       </c>
@@ -4525,11 +4229,11 @@
       <c r="AJ23" s="9"/>
     </row>
     <row r="24" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="77" t="str">
+      <c r="A24" s="82" t="str">
         <f>IF(K21="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="B24" s="77"/>
+      <c r="B24" s="82"/>
       <c r="C24" s="37" t="str">
         <v>Ivory Coast</v>
       </c>
@@ -4584,11 +4288,11 @@
         <f>F_Team2</f>
         <v>Japan</v>
       </c>
-      <c r="Y24" s="77" t="str">
+      <c r="Y24" s="82" t="str">
         <f>IF(AI21="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="Z24" s="77"/>
+      <c r="Z24" s="82"/>
       <c r="AA24" s="37" t="str">
         <v>Sweden</v>
       </c>
@@ -4617,11 +4321,11 @@
       <c r="AJ24" s="9"/>
     </row>
     <row r="25" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="77" t="str">
+      <c r="A25" s="82" t="str">
         <f>IF(K21="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="B25" s="77"/>
+      <c r="B25" s="82"/>
       <c r="C25" s="46" t="str">
         <v>Ecuador</v>
       </c>
@@ -4676,11 +4380,11 @@
         <f>F_Team3</f>
         <v>Sweden</v>
       </c>
-      <c r="Y25" s="77" t="str">
+      <c r="Y25" s="82" t="str">
         <f>IF(AI21="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="Z25" s="77"/>
+      <c r="Z25" s="82"/>
       <c r="AA25" s="46" t="str">
         <v>Tunisia</v>
       </c>
@@ -4807,14 +4511,8 @@
       <c r="AJ27" s="52"/>
     </row>
     <row r="28" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="str">
-        <f>IF(OR(AND(J31=3,J32=3,J33=3,J34=3),AND(B28="ties",K30="GROUP COMPLETE")),"TIES","OK")</f>
-        <v>OK</v>
-      </c>
-      <c r="B28" s="2" t="str">
-        <f>IF([1]GroupG!$AG$6=10,"",IF(AND([1]GroupG!$AN$6&lt;&gt;24,[1]GroupG!$AJ$6&lt;&gt;24,[1]GroupG!$AG$6&lt;&gt;24,OR([1]GroupG!$AT$6=10,[1]GroupG!$AU$6=10)),"ties","group good"))</f>
-        <v>group good</v>
-      </c>
+      <c r="A28" s="1"/>
+      <c r="B28" s="2"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -4825,30 +4523,24 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="4"/>
-      <c r="M28" s="78" t="s">
+      <c r="M28" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="N28" s="78"/>
-      <c r="O28" s="78"/>
-      <c r="P28" s="78"/>
-      <c r="Q28" s="78"/>
+      <c r="N28" s="83"/>
+      <c r="O28" s="83"/>
+      <c r="P28" s="83"/>
+      <c r="Q28" s="83"/>
       <c r="R28" s="59"/>
       <c r="S28" s="14"/>
-      <c r="T28" s="79" t="s">
+      <c r="T28" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="U28" s="79"/>
-      <c r="V28" s="79"/>
-      <c r="W28" s="79"/>
-      <c r="X28" s="79"/>
-      <c r="Y28" s="1" t="str">
-        <f>IF(OR(AND(AH31=3,AH32=3,AH33=3,AH34=3),AND(Z28="ties",AI30="GROUP COMPLETE")),"TIES","OK")</f>
-        <v>OK</v>
-      </c>
-      <c r="Z28" s="2" t="str">
-        <f>IF([1]GroupH!$AG$6=10,"",IF(AND([1]GroupH!$AN$6&lt;&gt;24,[1]GroupH!$AJ$6&lt;&gt;24,[1]GroupH!$AG$6&lt;&gt;24,OR([1]GroupH!$AT$6=10,[1]GroupH!$AU$6=10)),"ties","group good"))</f>
-        <v/>
-      </c>
+      <c r="U28" s="84"/>
+      <c r="V28" s="84"/>
+      <c r="W28" s="84"/>
+      <c r="X28" s="84"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="2"/>
       <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
@@ -4863,16 +4555,16 @@
     <row r="29" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7"/>
       <c r="B29" s="8"/>
-      <c r="C29" s="80" t="s">
+      <c r="C29" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="80"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="80"/>
-      <c r="G29" s="80"/>
-      <c r="H29" s="80"/>
-      <c r="I29" s="80"/>
-      <c r="J29" s="80"/>
+      <c r="D29" s="85"/>
+      <c r="E29" s="85"/>
+      <c r="F29" s="85"/>
+      <c r="G29" s="85"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="85"/>
+      <c r="J29" s="85"/>
       <c r="K29" s="8"/>
       <c r="L29" s="9"/>
       <c r="M29" s="60"/>
@@ -4889,16 +4581,16 @@
       <c r="X29" s="16"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="8"/>
-      <c r="AA29" s="80" t="s">
+      <c r="AA29" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="AB29" s="80"/>
-      <c r="AC29" s="80"/>
-      <c r="AD29" s="80"/>
-      <c r="AE29" s="80"/>
-      <c r="AF29" s="80"/>
-      <c r="AG29" s="80"/>
-      <c r="AH29" s="80"/>
+      <c r="AB29" s="85"/>
+      <c r="AC29" s="85"/>
+      <c r="AD29" s="85"/>
+      <c r="AE29" s="85"/>
+      <c r="AF29" s="85"/>
+      <c r="AG29" s="85"/>
+      <c r="AH29" s="85"/>
       <c r="AI29" s="8"/>
       <c r="AJ29" s="9"/>
     </row>
@@ -4995,11 +4687,11 @@
       <c r="AJ30" s="9"/>
     </row>
     <row r="31" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="77" t="str">
+      <c r="A31" s="82" t="str">
         <f>IF(K30="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="B31" s="77"/>
+      <c r="B31" s="82"/>
       <c r="C31" s="33" t="str" cm="1">
         <f t="array" ref="C31:J34">_xlfn._xlws.SORT(C79:J82,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Belgium</v>
@@ -5055,11 +4747,11 @@
         <f>H_Team2</f>
         <v>Cabo Verde</v>
       </c>
-      <c r="Y31" s="77" t="str">
+      <c r="Y31" s="82" t="str">
         <f>IF(AI30="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="Z31" s="77"/>
+      <c r="Z31" s="82"/>
       <c r="AA31" s="37" t="str" cm="1">
         <f t="array" ref="AA31:AH34">_xlfn._xlws.SORT(AA79:AH82,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Spain</v>
@@ -5089,11 +4781,11 @@
       <c r="AJ31" s="9"/>
     </row>
     <row r="32" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="77" t="str">
+      <c r="A32" s="82" t="str">
         <f>IF(K30="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="B32" s="77"/>
+      <c r="B32" s="82"/>
       <c r="C32" s="37" t="str">
         <v>Egypt</v>
       </c>
@@ -5148,11 +4840,11 @@
         <f>H_Team2</f>
         <v>Cabo Verde</v>
       </c>
-      <c r="Y32" s="77" t="str">
+      <c r="Y32" s="82" t="str">
         <f>IF(AI30="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="Z32" s="77"/>
+      <c r="Z32" s="82"/>
       <c r="AA32" s="37" t="str">
         <v>Cabo Verde</v>
       </c>
@@ -5181,11 +4873,11 @@
       <c r="AJ32" s="9"/>
     </row>
     <row r="33" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="77" t="str">
+      <c r="A33" s="82" t="str">
         <f>IF(K30="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="B33" s="77"/>
+      <c r="B33" s="82"/>
       <c r="C33" s="37" t="str">
         <v>Iran</v>
       </c>
@@ -5240,11 +4932,11 @@
         <f>H_Team3</f>
         <v>Saudi Arabia</v>
       </c>
-      <c r="Y33" s="77" t="str">
+      <c r="Y33" s="82" t="str">
         <f>IF(AI30="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="Z33" s="77"/>
+      <c r="Z33" s="82"/>
       <c r="AA33" s="37" t="str">
         <v>Saudi Arabia</v>
       </c>
@@ -5273,11 +4965,11 @@
       <c r="AJ33" s="9"/>
     </row>
     <row r="34" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="77" t="str">
+      <c r="A34" s="82" t="str">
         <f>IF(K30="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="B34" s="77"/>
+      <c r="B34" s="82"/>
       <c r="C34" s="46" t="str">
         <v>New Zealand</v>
       </c>
@@ -5332,11 +5024,11 @@
         <f>H_Team3</f>
         <v>Saudi Arabia</v>
       </c>
-      <c r="Y34" s="77" t="str">
+      <c r="Y34" s="82" t="str">
         <f>IF(AI30="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="Z34" s="77"/>
+      <c r="Z34" s="82"/>
       <c r="AA34" s="46" t="str">
         <v>Uruguay</v>
       </c>
@@ -5463,14 +5155,8 @@
       <c r="AJ36" s="52"/>
     </row>
     <row r="37" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="str">
-        <f>IF(OR(AND(J40=3,J41=3,J42=3,J43=3),AND(B37="ties",K39="GROUP COMPLETE")),"TIES","OK")</f>
-        <v>OK</v>
-      </c>
-      <c r="B37" s="2" t="str">
-        <f>IF([1]GroupI!$AG$6=10,"",IF(AND([1]GroupI!$AN$6&lt;&gt;24,[1]GroupI!$AJ$6&lt;&gt;24,[1]GroupI!$AG$6&lt;&gt;24,OR([1]GroupI!$AT$6=10,[1]GroupI!$AU$6=10)),"ties","group good"))</f>
-        <v/>
-      </c>
+      <c r="A37" s="1"/>
+      <c r="B37" s="2"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -5481,30 +5167,24 @@
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="4"/>
-      <c r="M37" s="78" t="s">
+      <c r="M37" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="N37" s="78"/>
-      <c r="O37" s="78"/>
-      <c r="P37" s="78"/>
-      <c r="Q37" s="78"/>
+      <c r="N37" s="83"/>
+      <c r="O37" s="83"/>
+      <c r="P37" s="83"/>
+      <c r="Q37" s="83"/>
       <c r="R37" s="59"/>
       <c r="S37" s="14"/>
-      <c r="T37" s="79" t="s">
+      <c r="T37" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="U37" s="79"/>
-      <c r="V37" s="79"/>
-      <c r="W37" s="79"/>
-      <c r="X37" s="79"/>
-      <c r="Y37" s="1" t="str">
-        <f>IF(OR(AND(AH40=3,AH41=3,AH42=3,AH43=3),AND(Z37="ties",AI39="GROUP COMPLETE")),"TIES","OK")</f>
-        <v>OK</v>
-      </c>
-      <c r="Z37" s="2" t="str">
-        <f>IF([1]GroupJ!$AG$6=10,"",IF(AND([1]GroupJ!$AN$6&lt;&gt;24,[1]GroupJ!$AJ$6&lt;&gt;24,[1]GroupJ!$AG$6&lt;&gt;24,OR([1]GroupJ!$AT$6=10,[1]GroupJ!$AU$6=10)),"ties","group good"))</f>
-        <v>group good</v>
-      </c>
+      <c r="U37" s="84"/>
+      <c r="V37" s="84"/>
+      <c r="W37" s="84"/>
+      <c r="X37" s="84"/>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="2"/>
       <c r="AA37" s="3"/>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
@@ -5519,16 +5199,16 @@
     <row r="38" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7"/>
       <c r="B38" s="8"/>
-      <c r="C38" s="80" t="s">
+      <c r="C38" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="D38" s="80"/>
-      <c r="E38" s="80"/>
-      <c r="F38" s="80"/>
-      <c r="G38" s="80"/>
-      <c r="H38" s="80"/>
-      <c r="I38" s="80"/>
-      <c r="J38" s="80"/>
+      <c r="D38" s="85"/>
+      <c r="E38" s="85"/>
+      <c r="F38" s="85"/>
+      <c r="G38" s="85"/>
+      <c r="H38" s="85"/>
+      <c r="I38" s="85"/>
+      <c r="J38" s="85"/>
       <c r="K38" s="8"/>
       <c r="L38" s="9"/>
       <c r="M38" s="60"/>
@@ -5545,16 +5225,16 @@
       <c r="X38" s="16"/>
       <c r="Y38" s="7"/>
       <c r="Z38" s="8"/>
-      <c r="AA38" s="80" t="s">
+      <c r="AA38" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="AB38" s="80"/>
-      <c r="AC38" s="80"/>
-      <c r="AD38" s="80"/>
-      <c r="AE38" s="80"/>
-      <c r="AF38" s="80"/>
-      <c r="AG38" s="80"/>
-      <c r="AH38" s="80"/>
+      <c r="AB38" s="85"/>
+      <c r="AC38" s="85"/>
+      <c r="AD38" s="85"/>
+      <c r="AE38" s="85"/>
+      <c r="AF38" s="85"/>
+      <c r="AG38" s="85"/>
+      <c r="AH38" s="85"/>
       <c r="AI38" s="8"/>
       <c r="AJ38" s="9"/>
     </row>
@@ -5651,11 +5331,11 @@
       <c r="AJ39" s="9"/>
     </row>
     <row r="40" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="77" t="str">
+      <c r="A40" s="82" t="str">
         <f>IF(K39="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="B40" s="77"/>
+      <c r="B40" s="82"/>
       <c r="C40" s="33" t="str" cm="1">
         <f t="array" ref="C40:J43">_xlfn._xlws.SORT(C86:J89,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>France</v>
@@ -5711,11 +5391,11 @@
         <f>J_Team4</f>
         <v>Jordan</v>
       </c>
-      <c r="Y40" s="77" t="str">
+      <c r="Y40" s="82" t="str">
         <f>IF(AI39="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="Z40" s="77"/>
+      <c r="Z40" s="82"/>
       <c r="AA40" s="37" t="str" cm="1">
         <f t="array" ref="AA40:AH43">_xlfn._xlws.SORT(AA86:AH89,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Argentina</v>
@@ -5745,11 +5425,11 @@
       <c r="AJ40" s="9"/>
     </row>
     <row r="41" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="77" t="str">
+      <c r="A41" s="82" t="str">
         <f>IF(K39="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="B41" s="77"/>
+      <c r="B41" s="82"/>
       <c r="C41" s="37" t="str">
         <v>Senegal</v>
       </c>
@@ -5804,11 +5484,11 @@
         <f>J_Team3</f>
         <v>Austria</v>
       </c>
-      <c r="Y41" s="77" t="str">
+      <c r="Y41" s="82" t="str">
         <f>IF(AI39="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="Z41" s="77"/>
+      <c r="Z41" s="82"/>
       <c r="AA41" s="37" t="str">
         <v>Algeria</v>
       </c>
@@ -5837,11 +5517,11 @@
       <c r="AJ41" s="9"/>
     </row>
     <row r="42" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="77" t="str">
+      <c r="A42" s="82" t="str">
         <f>IF(K39="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="B42" s="77"/>
+      <c r="B42" s="82"/>
       <c r="C42" s="37" t="str">
         <v>Iraq</v>
       </c>
@@ -5896,11 +5576,11 @@
         <f>J_Team2</f>
         <v>Algeria</v>
       </c>
-      <c r="Y42" s="77" t="str">
+      <c r="Y42" s="82" t="str">
         <f>IF(AI39="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="Z42" s="77"/>
+      <c r="Z42" s="82"/>
       <c r="AA42" s="37" t="str">
         <v>Austria</v>
       </c>
@@ -5929,11 +5609,11 @@
       <c r="AJ42" s="9"/>
     </row>
     <row r="43" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="77" t="str">
+      <c r="A43" s="82" t="str">
         <f>IF(K39="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="B43" s="77"/>
+      <c r="B43" s="82"/>
       <c r="C43" s="46" t="str">
         <v>Norway</v>
       </c>
@@ -5988,11 +5668,11 @@
         <f>J_Team3</f>
         <v>Austria</v>
       </c>
-      <c r="Y43" s="77" t="str">
+      <c r="Y43" s="82" t="str">
         <f>IF(AI39="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="Z43" s="77"/>
+      <c r="Z43" s="82"/>
       <c r="AA43" s="46" t="str">
         <v>Jordan</v>
       </c>
@@ -6119,14 +5799,8 @@
       <c r="AJ45" s="52"/>
     </row>
     <row r="46" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="str">
-        <f>IF(OR(AND(J49=3,J50=3,J51=3,J52=3),AND(B46="ties",K48="GROUP COMPLETE")),"TIES","OK")</f>
-        <v>OK</v>
-      </c>
-      <c r="B46" s="2" t="str">
-        <f>IF([1]GroupK!$AG$6=10,"",IF(AND([1]GroupK!$AN$6&lt;&gt;24,[1]GroupK!$AJ$6&lt;&gt;24,[1]GroupK!$AG$6&lt;&gt;24,OR([1]GroupK!$AT$6=10,[1]GroupK!$AU$6=10)),"ties","group good"))</f>
-        <v>group good</v>
-      </c>
+      <c r="A46" s="1"/>
+      <c r="B46" s="2"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -6137,30 +5811,24 @@
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="4"/>
-      <c r="M46" s="78" t="s">
+      <c r="M46" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="N46" s="78"/>
-      <c r="O46" s="78"/>
-      <c r="P46" s="78"/>
-      <c r="Q46" s="78"/>
+      <c r="N46" s="83"/>
+      <c r="O46" s="83"/>
+      <c r="P46" s="83"/>
+      <c r="Q46" s="83"/>
       <c r="R46" s="59"/>
       <c r="S46" s="14"/>
-      <c r="T46" s="79" t="s">
+      <c r="T46" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="U46" s="79"/>
-      <c r="V46" s="79"/>
-      <c r="W46" s="79"/>
-      <c r="X46" s="79"/>
-      <c r="Y46" s="1" t="str">
-        <f>IF(OR(AND(AH49=3,AH50=3,AH51=3,AH52=3),AND(Z46="ties",AI48="GROUP COMPLETE")),"TIES","OK")</f>
-        <v>OK</v>
-      </c>
-      <c r="Z46" s="2" t="str">
-        <f>IF([1]GroupL!$AG$6=10,"",IF(AND([1]GroupL!$AN$6&lt;&gt;24,[1]GroupL!$AJ$6&lt;&gt;24,[1]GroupL!$AG$6&lt;&gt;24,OR([1]GroupL!$AT$6=10,[1]GroupL!$AU$6=10)),"ties","group good"))</f>
-        <v/>
-      </c>
+      <c r="U46" s="84"/>
+      <c r="V46" s="84"/>
+      <c r="W46" s="84"/>
+      <c r="X46" s="84"/>
+      <c r="Y46" s="1"/>
+      <c r="Z46" s="2"/>
       <c r="AA46" s="3"/>
       <c r="AB46" s="3"/>
       <c r="AC46" s="3"/>
@@ -6175,16 +5843,16 @@
     <row r="47" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7"/>
       <c r="B47" s="8"/>
-      <c r="C47" s="80" t="s">
+      <c r="C47" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="D47" s="80"/>
-      <c r="E47" s="80"/>
-      <c r="F47" s="80"/>
-      <c r="G47" s="80"/>
-      <c r="H47" s="80"/>
-      <c r="I47" s="80"/>
-      <c r="J47" s="80"/>
+      <c r="D47" s="85"/>
+      <c r="E47" s="85"/>
+      <c r="F47" s="85"/>
+      <c r="G47" s="85"/>
+      <c r="H47" s="85"/>
+      <c r="I47" s="85"/>
+      <c r="J47" s="85"/>
       <c r="K47" s="8"/>
       <c r="L47" s="9"/>
       <c r="M47" s="60"/>
@@ -6201,16 +5869,16 @@
       <c r="X47" s="16"/>
       <c r="Y47" s="7"/>
       <c r="Z47" s="8"/>
-      <c r="AA47" s="80" t="s">
+      <c r="AA47" s="85" t="s">
         <v>32</v>
       </c>
-      <c r="AB47" s="80"/>
-      <c r="AC47" s="80"/>
-      <c r="AD47" s="80"/>
-      <c r="AE47" s="80"/>
-      <c r="AF47" s="80"/>
-      <c r="AG47" s="80"/>
-      <c r="AH47" s="80"/>
+      <c r="AB47" s="85"/>
+      <c r="AC47" s="85"/>
+      <c r="AD47" s="85"/>
+      <c r="AE47" s="85"/>
+      <c r="AF47" s="85"/>
+      <c r="AG47" s="85"/>
+      <c r="AH47" s="85"/>
       <c r="AI47" s="8"/>
       <c r="AJ47" s="9"/>
     </row>
@@ -6307,11 +5975,11 @@
       <c r="AJ48" s="9"/>
     </row>
     <row r="49" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="77" t="str">
+      <c r="A49" s="82" t="str">
         <f>IF(K48="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="B49" s="77"/>
+      <c r="B49" s="82"/>
       <c r="C49" s="33" t="str" cm="1">
         <f t="array" ref="C49:J52">_xlfn._xlws.SORT(C93:J96,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Portugal</v>
@@ -6367,11 +6035,11 @@
         <f>L_Team2</f>
         <v>Croatia</v>
       </c>
-      <c r="Y49" s="77" t="str">
+      <c r="Y49" s="82" t="str">
         <f>IF(AI48="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="Z49" s="77"/>
+      <c r="Z49" s="82"/>
       <c r="AA49" s="37" t="str" cm="1">
         <f t="array" ref="AA49:AH52">_xlfn._xlws.SORT(AA93:AH96,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>England</v>
@@ -6401,11 +6069,11 @@
       <c r="AJ49" s="9"/>
     </row>
     <row r="50" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="77" t="str">
+      <c r="A50" s="82" t="str">
         <f>IF(K48="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="B50" s="77"/>
+      <c r="B50" s="82"/>
       <c r="C50" s="37" t="str">
         <v>Congo</v>
       </c>
@@ -6460,11 +6128,11 @@
         <f>L_Team3</f>
         <v>Ghana</v>
       </c>
-      <c r="Y50" s="77" t="str">
+      <c r="Y50" s="82" t="str">
         <f>IF(AI48="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="Z50" s="77"/>
+      <c r="Z50" s="82"/>
       <c r="AA50" s="37" t="str">
         <v>Croatia</v>
       </c>
@@ -6493,11 +6161,11 @@
       <c r="AJ50" s="9"/>
     </row>
     <row r="51" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="77" t="str">
+      <c r="A51" s="82" t="str">
         <f>IF(K48="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="B51" s="77"/>
+      <c r="B51" s="82"/>
       <c r="C51" s="37" t="str">
         <v>Uzbekistan</v>
       </c>
@@ -6552,11 +6220,11 @@
         <f>L_Team2</f>
         <v>Croatia</v>
       </c>
-      <c r="Y51" s="77" t="str">
+      <c r="Y51" s="82" t="str">
         <f>IF(AI48="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="Z51" s="77"/>
+      <c r="Z51" s="82"/>
       <c r="AA51" s="37" t="str">
         <v>Ghana</v>
       </c>
@@ -6585,11 +6253,11 @@
       <c r="AJ51" s="9"/>
     </row>
     <row r="52" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="77" t="str">
+      <c r="A52" s="82" t="str">
         <f>IF(K48="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="B52" s="77"/>
+      <c r="B52" s="82"/>
       <c r="C52" s="46" t="str">
         <v>Colombia</v>
       </c>
@@ -6644,11 +6312,11 @@
         <f>L_Team1</f>
         <v>England</v>
       </c>
-      <c r="Y52" s="77" t="str">
+      <c r="Y52" s="82" t="str">
         <f>IF(AI48="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="Z52" s="77"/>
+      <c r="Z52" s="82"/>
       <c r="AA52" s="46" t="str">
         <v>Panama</v>
       </c>
@@ -6776,16 +6444,16 @@
     </row>
     <row r="56" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="75"/>
-      <c r="C56" s="82" t="s">
+      <c r="C56" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="D56" s="82"/>
-      <c r="E56" s="82"/>
-      <c r="F56" s="82"/>
-      <c r="G56" s="82"/>
-      <c r="H56" s="82"/>
-      <c r="I56" s="82"/>
-      <c r="J56" s="82"/>
+      <c r="D56" s="87"/>
+      <c r="E56" s="87"/>
+      <c r="F56" s="87"/>
+      <c r="G56" s="87"/>
+      <c r="H56" s="87"/>
+      <c r="I56" s="87"/>
+      <c r="J56" s="87"/>
       <c r="K56" s="75"/>
       <c r="L56" s="75"/>
       <c r="M56" s="75"/>
@@ -6802,16 +6470,16 @@
       <c r="X56" s="75"/>
       <c r="Y56" s="75"/>
       <c r="Z56" s="75"/>
-      <c r="AA56" s="82" t="s">
+      <c r="AA56" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="AB56" s="82"/>
-      <c r="AC56" s="82"/>
-      <c r="AD56" s="82"/>
-      <c r="AE56" s="82"/>
-      <c r="AF56" s="82"/>
-      <c r="AG56" s="82"/>
-      <c r="AH56" s="82"/>
+      <c r="AB56" s="87"/>
+      <c r="AC56" s="87"/>
+      <c r="AD56" s="87"/>
+      <c r="AE56" s="87"/>
+      <c r="AF56" s="87"/>
+      <c r="AG56" s="87"/>
+      <c r="AH56" s="87"/>
       <c r="AI56" s="75"/>
       <c r="AJ56" s="75"/>
     </row>
@@ -7017,7 +6685,7 @@
       <c r="Y59" s="75"/>
       <c r="Z59" s="75"/>
       <c r="AA59" s="75" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AB59" s="75" cm="1">
         <f t="array" ref="AB59">SUMPRODUCT((T$3:T$8=AA59)*(U$3:U$8&gt;W$3:W$8)) + SUMPRODUCT((X$3:X$8=AA59)*(W$3:W$8&gt;U$3:U$8))</f>
@@ -7136,7 +6804,7 @@
     <row r="61" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="75"/>
       <c r="C61" s="75" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D61" s="75" cm="1">
         <f t="array" ref="D61">SUMPRODUCT((M$3:M$8=C61)*(N$3:N$8&gt;P$3:P$8)) + SUMPRODUCT((Q$3:Q$8=C61)*(P$3:P$8&gt;N$3:N$8))</f>
@@ -7255,16 +6923,16 @@
     </row>
     <row r="63" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="75"/>
-      <c r="C63" s="82" t="s">
+      <c r="C63" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="D63" s="82"/>
-      <c r="E63" s="82"/>
-      <c r="F63" s="82"/>
-      <c r="G63" s="82"/>
-      <c r="H63" s="82"/>
-      <c r="I63" s="82"/>
-      <c r="J63" s="82"/>
+      <c r="D63" s="87"/>
+      <c r="E63" s="87"/>
+      <c r="F63" s="87"/>
+      <c r="G63" s="87"/>
+      <c r="H63" s="87"/>
+      <c r="I63" s="87"/>
+      <c r="J63" s="87"/>
       <c r="K63" s="75"/>
       <c r="L63" s="75"/>
       <c r="M63" s="75"/>
@@ -7281,16 +6949,16 @@
       <c r="X63" s="75"/>
       <c r="Y63" s="75"/>
       <c r="Z63" s="75"/>
-      <c r="AA63" s="82" t="s">
+      <c r="AA63" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="AB63" s="82"/>
-      <c r="AC63" s="82"/>
-      <c r="AD63" s="82"/>
-      <c r="AE63" s="82"/>
-      <c r="AF63" s="82"/>
-      <c r="AG63" s="82"/>
-      <c r="AH63" s="82"/>
+      <c r="AB63" s="87"/>
+      <c r="AC63" s="87"/>
+      <c r="AD63" s="87"/>
+      <c r="AE63" s="87"/>
+      <c r="AF63" s="87"/>
+      <c r="AG63" s="87"/>
+      <c r="AH63" s="87"/>
       <c r="AI63" s="75"/>
       <c r="AJ63" s="75"/>
     </row>
@@ -7734,16 +7402,16 @@
     </row>
     <row r="70" spans="2:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="75"/>
-      <c r="C70" s="82" t="s">
+      <c r="C70" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="D70" s="82"/>
-      <c r="E70" s="82"/>
-      <c r="F70" s="82"/>
-      <c r="G70" s="82"/>
-      <c r="H70" s="82"/>
-      <c r="I70" s="82"/>
-      <c r="J70" s="82"/>
+      <c r="D70" s="87"/>
+      <c r="E70" s="87"/>
+      <c r="F70" s="87"/>
+      <c r="G70" s="87"/>
+      <c r="H70" s="87"/>
+      <c r="I70" s="87"/>
+      <c r="J70" s="87"/>
       <c r="K70" s="75"/>
       <c r="L70" s="75"/>
       <c r="M70" s="75"/>
@@ -7760,16 +7428,16 @@
       <c r="X70" s="75"/>
       <c r="Y70" s="75"/>
       <c r="Z70" s="75"/>
-      <c r="AA70" s="82" t="s">
+      <c r="AA70" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="AB70" s="82"/>
-      <c r="AC70" s="82"/>
-      <c r="AD70" s="82"/>
-      <c r="AE70" s="82"/>
-      <c r="AF70" s="82"/>
-      <c r="AG70" s="82"/>
-      <c r="AH70" s="82"/>
+      <c r="AB70" s="87"/>
+      <c r="AC70" s="87"/>
+      <c r="AD70" s="87"/>
+      <c r="AE70" s="87"/>
+      <c r="AF70" s="87"/>
+      <c r="AG70" s="87"/>
+      <c r="AH70" s="87"/>
       <c r="AI70" s="75"/>
       <c r="AJ70" s="75"/>
     </row>
@@ -8058,7 +7726,7 @@
       <c r="Y74" s="75"/>
       <c r="Z74" s="75"/>
       <c r="AA74" s="75" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AB74" s="75" cm="1">
         <f t="array" ref="AB74">SUMPRODUCT((T$21:T$26=AA74)*(U$21:U$26&gt;W$21:W$26)) + SUMPRODUCT((X$21:X$26=AA74)*(W$21:W$26&gt;U$21:U$26))</f>
@@ -8213,16 +7881,16 @@
     </row>
     <row r="77" spans="2:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="75"/>
-      <c r="C77" s="82" t="s">
+      <c r="C77" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="D77" s="82"/>
-      <c r="E77" s="82"/>
-      <c r="F77" s="82"/>
-      <c r="G77" s="82"/>
-      <c r="H77" s="82"/>
-      <c r="I77" s="82"/>
-      <c r="J77" s="82"/>
+      <c r="D77" s="87"/>
+      <c r="E77" s="87"/>
+      <c r="F77" s="87"/>
+      <c r="G77" s="87"/>
+      <c r="H77" s="87"/>
+      <c r="I77" s="87"/>
+      <c r="J77" s="87"/>
       <c r="K77" s="75"/>
       <c r="L77" s="75"/>
       <c r="M77" s="75"/>
@@ -8239,16 +7907,16 @@
       <c r="X77" s="75"/>
       <c r="Y77" s="75"/>
       <c r="Z77" s="75"/>
-      <c r="AA77" s="82" t="s">
+      <c r="AA77" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="AB77" s="82"/>
-      <c r="AC77" s="82"/>
-      <c r="AD77" s="82"/>
-      <c r="AE77" s="82"/>
-      <c r="AF77" s="82"/>
-      <c r="AG77" s="82"/>
-      <c r="AH77" s="82"/>
+      <c r="AB77" s="87"/>
+      <c r="AC77" s="87"/>
+      <c r="AD77" s="87"/>
+      <c r="AE77" s="87"/>
+      <c r="AF77" s="87"/>
+      <c r="AG77" s="87"/>
+      <c r="AH77" s="87"/>
       <c r="AI77" s="75"/>
       <c r="AJ77" s="75"/>
     </row>
@@ -8692,16 +8360,16 @@
     </row>
     <row r="84" spans="2:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="75"/>
-      <c r="C84" s="82" t="s">
+      <c r="C84" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="D84" s="82"/>
-      <c r="E84" s="82"/>
-      <c r="F84" s="82"/>
-      <c r="G84" s="82"/>
-      <c r="H84" s="82"/>
-      <c r="I84" s="82"/>
-      <c r="J84" s="82"/>
+      <c r="D84" s="87"/>
+      <c r="E84" s="87"/>
+      <c r="F84" s="87"/>
+      <c r="G84" s="87"/>
+      <c r="H84" s="87"/>
+      <c r="I84" s="87"/>
+      <c r="J84" s="87"/>
       <c r="K84" s="75"/>
       <c r="L84" s="75"/>
       <c r="M84" s="75"/>
@@ -8718,16 +8386,16 @@
       <c r="X84" s="75"/>
       <c r="Y84" s="75"/>
       <c r="Z84" s="75"/>
-      <c r="AA84" s="82" t="s">
+      <c r="AA84" s="87" t="s">
         <v>75</v>
       </c>
-      <c r="AB84" s="82"/>
-      <c r="AC84" s="82"/>
-      <c r="AD84" s="82"/>
-      <c r="AE84" s="82"/>
-      <c r="AF84" s="82"/>
-      <c r="AG84" s="82"/>
-      <c r="AH84" s="82"/>
+      <c r="AB84" s="87"/>
+      <c r="AC84" s="87"/>
+      <c r="AD84" s="87"/>
+      <c r="AE84" s="87"/>
+      <c r="AF84" s="87"/>
+      <c r="AG84" s="87"/>
+      <c r="AH84" s="87"/>
       <c r="AI84" s="75"/>
       <c r="AJ84" s="75"/>
     </row>
@@ -8969,7 +8637,7 @@
     <row r="88" spans="2:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="75"/>
       <c r="C88" s="75" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D88" s="75" cm="1">
         <f t="array" ref="D88">SUMPRODUCT((M$39:M$44=C88)*(N$39:N$44&gt;P$39:P$44)) + SUMPRODUCT((Q$39:Q$44=C88)*(P$39:P$44&gt;N$39:N$44))</f>
@@ -9171,16 +8839,16 @@
     </row>
     <row r="91" spans="2:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="75"/>
-      <c r="C91" s="82" t="s">
+      <c r="C91" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="D91" s="82"/>
-      <c r="E91" s="82"/>
-      <c r="F91" s="82"/>
-      <c r="G91" s="82"/>
-      <c r="H91" s="82"/>
-      <c r="I91" s="82"/>
-      <c r="J91" s="82"/>
+      <c r="D91" s="87"/>
+      <c r="E91" s="87"/>
+      <c r="F91" s="87"/>
+      <c r="G91" s="87"/>
+      <c r="H91" s="87"/>
+      <c r="I91" s="87"/>
+      <c r="J91" s="87"/>
       <c r="K91" s="75"/>
       <c r="L91" s="75"/>
       <c r="M91" s="75"/>
@@ -9197,16 +8865,16 @@
       <c r="X91" s="75"/>
       <c r="Y91" s="75"/>
       <c r="Z91" s="75"/>
-      <c r="AA91" s="82" t="s">
+      <c r="AA91" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="AB91" s="82"/>
-      <c r="AC91" s="82"/>
-      <c r="AD91" s="82"/>
-      <c r="AE91" s="82"/>
-      <c r="AF91" s="82"/>
-      <c r="AG91" s="82"/>
-      <c r="AH91" s="82"/>
+      <c r="AB91" s="87"/>
+      <c r="AC91" s="87"/>
+      <c r="AD91" s="87"/>
+      <c r="AE91" s="87"/>
+      <c r="AF91" s="87"/>
+      <c r="AG91" s="87"/>
+      <c r="AH91" s="87"/>
       <c r="AI91" s="75"/>
       <c r="AJ91" s="75"/>
     </row>
@@ -11499,7 +11167,7 @@
       <c r="AI148" s="75"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="RqGomAjCA4au9uWCvuiyoEqS2aA4eVkDOpddh0ErTedJGr2w134/EgrZ4tVvRjWb5FBtYsq3/9JMuX7D9DAh9A==" saltValue="nJWpfmLvfM0pNtyqf/I/mQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="B+NtaP2bSS+nOzTrZIVN09CxAFAiyHWrhWLWfxVNq+MVii/WvRxUfod1NbtbmL586RXjoNm4Q5pHL5n1UFkkdQ==" saltValue="hzAiQmnv2quOfKpmhwhUpg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="84">
     <mergeCell ref="C91:J91"/>
     <mergeCell ref="AA56:AH56"/>
@@ -11784,21 +11452,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="86"/>
-      <c r="L1" s="86"/>
-      <c r="M1" s="86"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
     </row>
     <row r="2" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="72"/>
@@ -11811,12 +11479,12 @@
       <c r="H2" s="73"/>
       <c r="I2" s="73"/>
       <c r="J2" s="73"/>
-      <c r="K2" s="87" t="str">
+      <c r="K2" s="81" t="str">
         <f>"Completed ("&amp;SUM(20-SUM(COUNTIF(J4,"")+COUNTIF(J6,"")+COUNTIF(I8,"")+COUNTIF(I10,"")+COUNTIF(J12,"")+COUNTIF(K14,"")+COUNTIF(K16,"")+COUNTIF(G18,"")+COUNTIF(H20,"")+COUNTIF(K22,"")+COUNTIF(L24,"&lt;=0")+COUNTIF(I26,"")+COUNTIF(J28,"")+COUNTIF(I30,"")+COUNTIF(I32,"")+COUNTIF(H34,"")+COUNTIF(I36,"")+COUNTIF(I38,"")+COUNTIF(H40,"")+COUNTIF(H42,"")))&amp;" out of 20)"</f>
         <v>Completed (1 out of 20)</v>
       </c>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="64"/>
@@ -11845,9 +11513,9 @@
       <c r="G4" s="64"/>
       <c r="H4" s="64"/>
       <c r="I4" s="64"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="85"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="78"/>
+      <c r="L4" s="79"/>
       <c r="M4" s="64"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -11877,9 +11545,9 @@
       <c r="G6" s="64"/>
       <c r="H6" s="64"/>
       <c r="I6" s="64"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="84"/>
-      <c r="L6" s="85"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="78"/>
+      <c r="L6" s="79"/>
       <c r="M6" s="64"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -11908,9 +11576,9 @@
       <c r="F8" s="64"/>
       <c r="G8" s="64"/>
       <c r="H8" s="64"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="84"/>
-      <c r="K8" s="85"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="78"/>
+      <c r="K8" s="79"/>
       <c r="L8" s="64"/>
       <c r="M8" s="64"/>
     </row>
@@ -11940,9 +11608,9 @@
       <c r="F10" s="64"/>
       <c r="G10" s="64"/>
       <c r="H10" s="64"/>
-      <c r="I10" s="83"/>
-      <c r="J10" s="84"/>
-      <c r="K10" s="85"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="78"/>
+      <c r="K10" s="79"/>
       <c r="L10" s="64"/>
       <c r="M10" s="64"/>
     </row>
@@ -12006,9 +11674,9 @@
       <c r="H14" s="64"/>
       <c r="I14" s="64"/>
       <c r="J14" s="64"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="84"/>
-      <c r="M14" s="85"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="78"/>
+      <c r="M14" s="79"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="64"/>
@@ -12038,9 +11706,9 @@
       <c r="H16" s="64"/>
       <c r="I16" s="64"/>
       <c r="J16" s="64"/>
-      <c r="K16" s="83"/>
-      <c r="L16" s="84"/>
-      <c r="M16" s="85"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="78"/>
+      <c r="M16" s="79"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="64"/>
@@ -12134,9 +11802,9 @@
       <c r="H22" s="64"/>
       <c r="I22" s="64"/>
       <c r="J22" s="64"/>
-      <c r="K22" s="83"/>
-      <c r="L22" s="84"/>
-      <c r="M22" s="85"/>
+      <c r="K22" s="77"/>
+      <c r="L22" s="78"/>
+      <c r="M22" s="79"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="64"/>
@@ -12155,7 +11823,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="64" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B24" s="64"/>
       <c r="C24" s="64"/>
@@ -12232,8 +11900,8 @@
       <c r="G28" s="64"/>
       <c r="H28" s="64"/>
       <c r="I28" s="64"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="85"/>
+      <c r="J28" s="77"/>
+      <c r="K28" s="79"/>
       <c r="L28" s="64"/>
       <c r="M28" s="64"/>
     </row>
@@ -12359,9 +12027,9 @@
       <c r="F36" s="64"/>
       <c r="G36" s="64"/>
       <c r="H36" s="64"/>
-      <c r="I36" s="83"/>
-      <c r="J36" s="84"/>
-      <c r="K36" s="85"/>
+      <c r="I36" s="77"/>
+      <c r="J36" s="78"/>
+      <c r="K36" s="79"/>
       <c r="L36" s="64"/>
       <c r="M36" s="64"/>
     </row>
@@ -12391,10 +12059,10 @@
       <c r="F38" s="64"/>
       <c r="G38" s="64"/>
       <c r="H38" s="64"/>
-      <c r="I38" s="83"/>
-      <c r="J38" s="84"/>
-      <c r="K38" s="84"/>
-      <c r="L38" s="85"/>
+      <c r="I38" s="77"/>
+      <c r="J38" s="78"/>
+      <c r="K38" s="78"/>
+      <c r="L38" s="79"/>
       <c r="M38" s="64"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
@@ -12422,10 +12090,10 @@
       <c r="E40" s="64"/>
       <c r="F40" s="64"/>
       <c r="G40" s="64"/>
-      <c r="H40" s="83"/>
-      <c r="I40" s="84"/>
-      <c r="J40" s="84"/>
-      <c r="K40" s="85"/>
+      <c r="H40" s="77"/>
+      <c r="I40" s="78"/>
+      <c r="J40" s="78"/>
+      <c r="K40" s="79"/>
       <c r="L40" s="64"/>
       <c r="M40" s="64"/>
     </row>
@@ -12454,10 +12122,10 @@
       <c r="E42" s="64"/>
       <c r="F42" s="64"/>
       <c r="G42" s="64"/>
-      <c r="H42" s="83"/>
-      <c r="I42" s="84"/>
-      <c r="J42" s="84"/>
-      <c r="K42" s="85"/>
+      <c r="H42" s="77"/>
+      <c r="I42" s="78"/>
+      <c r="J42" s="78"/>
+      <c r="K42" s="79"/>
       <c r="L42" s="64"/>
       <c r="M42" s="64"/>
     </row>
@@ -12503,7 +12171,7 @@
       <c r="G47" s="67"/>
       <c r="H47" s="67"/>
       <c r="I47" s="67" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J47" s="67"/>
       <c r="K47" s="67"/>
@@ -12570,10 +12238,10 @@
         <v>Argentina</v>
       </c>
       <c r="H49" s="65" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I49" s="65" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J49" s="67"/>
       <c r="K49" s="67"/>
@@ -12604,10 +12272,10 @@
         <v>Australia</v>
       </c>
       <c r="H50" s="65" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I50" s="65" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J50" s="67"/>
       <c r="K50" s="67"/>
@@ -12904,10 +12572,10 @@
         <v>Croatia</v>
       </c>
       <c r="H59" s="65" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I59" s="65" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J59" s="67"/>
       <c r="K59" s="67"/>
@@ -13096,10 +12764,10 @@
         <v>France</v>
       </c>
       <c r="H65" s="65" t="s">
-        <v>139</v>
+        <v>200</v>
       </c>
       <c r="I65" s="65" t="s">
-        <v>139</v>
+        <v>200</v>
       </c>
       <c r="J65" s="67"/>
       <c r="K65" s="67"/>
@@ -13128,10 +12796,10 @@
         <v>Germany</v>
       </c>
       <c r="H66" s="65" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I66" s="65" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J66" s="67"/>
       <c r="K66" s="67"/>
@@ -13160,10 +12828,10 @@
         <v>Ghana</v>
       </c>
       <c r="H67" s="65" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I67" s="65" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J67" s="67"/>
       <c r="K67" s="67"/>
@@ -13192,10 +12860,10 @@
         <v>Haiti</v>
       </c>
       <c r="H68" s="65" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I68" s="65" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J68" s="67"/>
       <c r="K68" s="67"/>
@@ -13224,10 +12892,10 @@
         <v>Iran</v>
       </c>
       <c r="H69" s="65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I69" s="65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J69" s="67"/>
       <c r="K69" s="67"/>
@@ -13256,10 +12924,10 @@
         <v>Bosnia</v>
       </c>
       <c r="H70" s="65" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I70" s="65" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J70" s="67"/>
       <c r="K70" s="67"/>
@@ -13288,10 +12956,10 @@
         <v>Ivory Coast</v>
       </c>
       <c r="H71" s="68" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I71" s="68" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J71" s="67"/>
       <c r="K71" s="67"/>
@@ -13320,10 +12988,10 @@
         <v>Japan</v>
       </c>
       <c r="H72" s="68" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I72" s="68" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J72" s="67"/>
       <c r="K72" s="67"/>
@@ -13352,10 +13020,10 @@
         <v>Jordan</v>
       </c>
       <c r="H73" s="68" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I73" s="68" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J73" s="67"/>
       <c r="K73" s="67"/>
@@ -13384,10 +13052,10 @@
         <v>South Korea</v>
       </c>
       <c r="H74" s="68" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I74" s="68" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J74" s="67"/>
       <c r="K74" s="67"/>
@@ -13416,10 +13084,10 @@
         <v>Mexico</v>
       </c>
       <c r="H75" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I75" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J75" s="67"/>
       <c r="K75" s="67"/>
@@ -13448,10 +13116,10 @@
         <v>Morocco</v>
       </c>
       <c r="H76" s="68" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I76" s="68" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J76" s="67"/>
       <c r="K76" s="67"/>
@@ -13480,10 +13148,10 @@
         <v>Netherlands</v>
       </c>
       <c r="H77" s="68" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I77" s="68" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J77" s="67"/>
       <c r="K77" s="67"/>
@@ -13512,10 +13180,10 @@
         <v>New Zealand</v>
       </c>
       <c r="H78" s="68" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I78" s="68" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J78" s="67"/>
       <c r="K78" s="67"/>
@@ -13544,10 +13212,10 @@
         <v>Norway</v>
       </c>
       <c r="H79" s="68" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I79" s="68" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J79" s="67"/>
       <c r="K79" s="67"/>
@@ -13576,10 +13244,10 @@
         <v>Panama</v>
       </c>
       <c r="H80" s="68" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I80" s="68" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J80" s="67"/>
       <c r="K80" s="67"/>
@@ -13608,10 +13276,10 @@
         <v>Paraguay</v>
       </c>
       <c r="H81" s="68" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I81" s="68" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J81" s="67"/>
       <c r="K81" s="67"/>
@@ -13640,10 +13308,10 @@
         <v>Sweden</v>
       </c>
       <c r="H82" s="68" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I82" s="68" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J82" s="67"/>
       <c r="K82" s="67"/>
@@ -13672,10 +13340,10 @@
         <v>Portugal</v>
       </c>
       <c r="H83" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I83" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J83" s="67"/>
       <c r="K83" s="67"/>
@@ -13704,10 +13372,10 @@
         <v>Qatar</v>
       </c>
       <c r="H84" s="68" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I84" s="68" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J84" s="67"/>
       <c r="K84" s="67"/>
@@ -13736,10 +13404,10 @@
         <v>Saudi Arabia</v>
       </c>
       <c r="H85" s="68" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I85" s="68" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J85" s="67"/>
       <c r="K85" s="67"/>
@@ -13768,10 +13436,10 @@
         <v>Scotland</v>
       </c>
       <c r="H86" s="68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I86" s="68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J86" s="67"/>
       <c r="K86" s="67"/>
@@ -13800,10 +13468,10 @@
         <v>Senegal</v>
       </c>
       <c r="H87" s="68" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I87" s="68" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J87" s="67"/>
       <c r="K87" s="67"/>
@@ -13832,10 +13500,10 @@
         <v>South Africa</v>
       </c>
       <c r="H88" s="68" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I88" s="68" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J88" s="67"/>
       <c r="K88" s="67"/>
@@ -13864,10 +13532,10 @@
         <v>Spain</v>
       </c>
       <c r="H89" s="68" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="I89" s="68" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="J89" s="67"/>
       <c r="K89" s="67"/>
@@ -13896,10 +13564,10 @@
         <v>Switzerland</v>
       </c>
       <c r="H90" s="68" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I90" s="68" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J90" s="67"/>
       <c r="K90" s="67"/>
@@ -13928,10 +13596,10 @@
         <v>Tunisia</v>
       </c>
       <c r="H91" s="68" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I91" s="68" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J91" s="67"/>
       <c r="K91" s="67"/>
@@ -13960,10 +13628,10 @@
         <v>Turkey</v>
       </c>
       <c r="H92" s="68" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I92" s="68" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J92" s="67"/>
       <c r="K92" s="67"/>
@@ -13992,10 +13660,10 @@
         <v>Uruguay</v>
       </c>
       <c r="H93" s="68" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I93" s="68" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J93" s="67"/>
       <c r="K93" s="67"/>
@@ -14024,10 +13692,10 @@
         <v>USA</v>
       </c>
       <c r="H94" s="68" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I94" s="68" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J94" s="67"/>
       <c r="K94" s="67"/>
@@ -14056,10 +13724,10 @@
         <v>Uzbekistan</v>
       </c>
       <c r="H95" s="68" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I95" s="68" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J95" s="67"/>
       <c r="K95" s="67"/>
@@ -14073,10 +13741,10 @@
       <c r="F96" s="67"/>
       <c r="G96" s="67"/>
       <c r="H96" s="68" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I96" s="68" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J96" s="67"/>
       <c r="K96" s="67"/>
@@ -14090,10 +13758,10 @@
       <c r="F97" s="67"/>
       <c r="G97" s="67"/>
       <c r="H97" s="68" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I97" s="68" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J97" s="67"/>
       <c r="K97" s="67"/>
@@ -14107,10 +13775,10 @@
       <c r="F98" s="67"/>
       <c r="G98" s="67"/>
       <c r="H98" s="68" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I98" s="68" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J98" s="67"/>
       <c r="K98" s="67"/>
@@ -14124,10 +13792,10 @@
       <c r="F99" s="67"/>
       <c r="G99" s="67"/>
       <c r="H99" s="68" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I99" s="68" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J99" s="67"/>
       <c r="K99" s="67"/>
@@ -14141,10 +13809,10 @@
       <c r="F100" s="67"/>
       <c r="G100" s="67"/>
       <c r="H100" s="68" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I100" s="68" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J100" s="67"/>
       <c r="K100" s="67"/>
@@ -14158,10 +13826,10 @@
       <c r="F101" s="67"/>
       <c r="G101" s="67"/>
       <c r="H101" s="68" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I101" s="68" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J101" s="67"/>
       <c r="K101" s="67"/>
@@ -14175,10 +13843,10 @@
       <c r="F102" s="67"/>
       <c r="G102" s="67"/>
       <c r="H102" s="68" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I102" s="68" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J102" s="67"/>
       <c r="K102" s="67"/>
@@ -14192,10 +13860,10 @@
       <c r="F103" s="67"/>
       <c r="G103" s="67"/>
       <c r="H103" s="68" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I103" s="68" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J103" s="67"/>
       <c r="K103" s="67"/>
@@ -14209,10 +13877,10 @@
       <c r="F104" s="67"/>
       <c r="G104" s="67"/>
       <c r="H104" s="68" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I104" s="68" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J104" s="67"/>
       <c r="K104" s="67"/>
@@ -14226,10 +13894,10 @@
       <c r="F105" s="67"/>
       <c r="G105" s="67"/>
       <c r="H105" s="68" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I105" s="68" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J105" s="67"/>
       <c r="K105" s="67"/>
@@ -14243,10 +13911,10 @@
       <c r="F106" s="67"/>
       <c r="G106" s="67"/>
       <c r="H106" s="68" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I106" s="68" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J106" s="67"/>
       <c r="K106" s="67"/>
@@ -14260,10 +13928,10 @@
       <c r="F107" s="67"/>
       <c r="G107" s="67"/>
       <c r="H107" s="68" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I107" s="68" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J107" s="67"/>
       <c r="K107" s="67"/>
@@ -14277,10 +13945,10 @@
       <c r="F108" s="67"/>
       <c r="G108" s="67"/>
       <c r="H108" s="68" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I108" s="68" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J108" s="67"/>
       <c r="K108" s="67"/>
@@ -14294,10 +13962,10 @@
       <c r="F109" s="67"/>
       <c r="G109" s="67"/>
       <c r="H109" s="68" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="I109" s="68" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="J109" s="67"/>
       <c r="K109" s="67"/>
@@ -14311,10 +13979,10 @@
       <c r="F110" s="67"/>
       <c r="G110" s="67"/>
       <c r="H110" s="68" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I110" s="68" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J110" s="67"/>
       <c r="K110" s="67"/>
@@ -14328,10 +13996,10 @@
       <c r="F111" s="67"/>
       <c r="G111" s="67"/>
       <c r="H111" s="68" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I111" s="68" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J111" s="67"/>
       <c r="K111" s="67"/>
@@ -14345,10 +14013,10 @@
       <c r="F112" s="67"/>
       <c r="G112" s="67"/>
       <c r="H112" s="68" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I112" s="68" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J112" s="67"/>
       <c r="K112" s="67"/>
@@ -14362,10 +14030,10 @@
       <c r="F113" s="67"/>
       <c r="G113" s="67"/>
       <c r="H113" s="68" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I113" s="68" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J113" s="67"/>
       <c r="K113" s="67"/>
@@ -14379,10 +14047,10 @@
       <c r="F114" s="67"/>
       <c r="G114" s="67"/>
       <c r="H114" s="68" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I114" s="68" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J114" s="67"/>
       <c r="K114" s="67"/>
@@ -14396,10 +14064,10 @@
       <c r="F115" s="67"/>
       <c r="G115" s="67"/>
       <c r="H115" s="68" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I115" s="68" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J115" s="67"/>
       <c r="K115" s="67"/>
@@ -14413,10 +14081,10 @@
       <c r="F116" s="67"/>
       <c r="G116" s="67"/>
       <c r="H116" s="68" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I116" s="68" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J116" s="67"/>
       <c r="K116" s="67"/>
@@ -14430,10 +14098,10 @@
       <c r="F117" s="67"/>
       <c r="G117" s="67"/>
       <c r="H117" s="68" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I117" s="68" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J117" s="67"/>
       <c r="K117" s="67"/>
@@ -14447,10 +14115,10 @@
       <c r="F118" s="67"/>
       <c r="G118" s="67"/>
       <c r="H118" s="68" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I118" s="68" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J118" s="67"/>
       <c r="K118" s="67"/>
@@ -14464,10 +14132,10 @@
       <c r="F119" s="67"/>
       <c r="G119" s="67"/>
       <c r="H119" s="68" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I119" s="68" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="J119" s="67"/>
       <c r="K119" s="67"/>
@@ -14506,7 +14174,7 @@
       <c r="J124" s="74"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="GvHqKQ4JtC3ruYfz2947+HLbzqOTw0b2wdWYb5lXlhXb0LsAm/ybIFQIQP37HjWD1iFP6fumJpaYuVPXM8QwsQ==" saltValue="jUVS5oZm/62uA2vKhMx8Hg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="s9Ci2VzJH+lZ+r08cGeqmIapFk6ZHOOcOf7qCQPvdUeHRRLkh9GAflBQHTVZv4//qek8JBmtZjy0zm1fsV2Lpw==" saltValue="nyvkWJ8TvmZtXlln8547DA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="14">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="K2:M2"/>

--- a/downloads/WC2026-GROUPS-BONUS.xlsx
+++ b/downloads/WC2026-GROUPS-BONUS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bob\Desktop\wc2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71CB0336-0C42-456E-B0DC-0297AACE4AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AFE16AB-E6CF-4292-857A-B01A30BD5DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="HiDxC2zhGT3wfx+5QZRw1x4pNxpSD7Thht9s43AhnOgV4JR+pqxyoVxeHHDhNa0gG0EVs2c6Wd+T4D4bjRr3Ag==" workbookSaltValue="PrnP9sc2NIUodcWwYN2RWg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{74C112C2-5EB1-4FE2-B062-25000C577A87}"/>
@@ -561,9 +561,6 @@
     <t>Canada vs Qatar</t>
   </si>
   <si>
-    <t>Mexico vs Korea</t>
-  </si>
-  <si>
     <t>USA vs Australia</t>
   </si>
   <si>
@@ -627,9 +624,6 @@
     <t>Morocco vs Haiti</t>
   </si>
   <si>
-    <t>South Africa vs Korea</t>
-  </si>
-  <si>
     <t>Curacao vs Ivory Coast</t>
   </si>
   <si>
@@ -700,9 +694,6 @@
   </si>
   <si>
     <t>Bosnia vs Qatar</t>
-  </si>
-  <si>
-    <t>Korea vs Czechia</t>
   </si>
   <si>
     <t>Czechia vs South Africa</t>
@@ -750,6 +741,15 @@
   </si>
   <si>
     <t>Senegal vs Iraq</t>
+  </si>
+  <si>
+    <t>South Korea vs Czechia</t>
+  </si>
+  <si>
+    <t>Mexico vs South Korea</t>
+  </si>
+  <si>
+    <t>South Africa vs South Korea</t>
   </si>
 </sst>
 </file>
@@ -1609,24 +1609,6 @@
     <xf numFmtId="0" fontId="14" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -1650,6 +1632,24 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2591,22 +2591,22 @@
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="4"/>
-      <c r="M1" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
+      <c r="M1" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
       <c r="R1" s="5"/>
       <c r="S1" s="6"/>
-      <c r="T1" s="83" t="s">
+      <c r="T1" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="U1" s="83"/>
-      <c r="V1" s="83"/>
-      <c r="W1" s="83"/>
-      <c r="X1" s="83"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="2"/>
       <c r="AA1" s="3"/>
@@ -2623,16 +2623,16 @@
     <row r="2" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
       <c r="K2" s="8"/>
       <c r="L2" s="9"/>
       <c r="M2" s="10"/>
@@ -2649,16 +2649,16 @@
       <c r="X2" s="16"/>
       <c r="Y2" s="7"/>
       <c r="Z2" s="8"/>
-      <c r="AA2" s="85" t="s">
+      <c r="AA2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="AB2" s="85"/>
-      <c r="AC2" s="85"/>
-      <c r="AD2" s="85"/>
-      <c r="AE2" s="85"/>
-      <c r="AF2" s="85"/>
-      <c r="AG2" s="85"/>
-      <c r="AH2" s="85"/>
+      <c r="AB2" s="80"/>
+      <c r="AC2" s="80"/>
+      <c r="AD2" s="80"/>
+      <c r="AE2" s="80"/>
+      <c r="AF2" s="80"/>
+      <c r="AG2" s="80"/>
+      <c r="AH2" s="80"/>
       <c r="AI2" s="8"/>
       <c r="AJ2" s="9"/>
     </row>
@@ -2755,11 +2755,11 @@
       <c r="AJ3" s="9"/>
     </row>
     <row r="4" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="82" t="str">
+      <c r="A4" s="77" t="str">
         <f>IF(K3="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="B4" s="82"/>
+      <c r="B4" s="77"/>
       <c r="C4" s="33" t="str" cm="1">
         <f t="array" ref="C4:J7">_xlfn._xlws.SORT(C58:J61,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Mexico</v>
@@ -2815,11 +2815,11 @@
         <f>B_Team4</f>
         <v>Switzerland</v>
       </c>
-      <c r="Y4" s="82" t="str">
+      <c r="Y4" s="77" t="str">
         <f>IF(AI3="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="Z4" s="82"/>
+      <c r="Z4" s="77"/>
       <c r="AA4" s="37" t="str" cm="1">
         <f t="array" ref="AA4:AH7">_xlfn._xlws.SORT(AA58:AH61,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Canada</v>
@@ -2849,11 +2849,11 @@
       <c r="AJ4" s="9"/>
     </row>
     <row r="5" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="82" t="str">
+      <c r="A5" s="77" t="str">
         <f>IF(K3="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="B5" s="82"/>
+      <c r="B5" s="77"/>
       <c r="C5" s="33" t="str">
         <v>South Africa</v>
       </c>
@@ -2908,11 +2908,11 @@
         <f>B_Team2</f>
         <v>Bosnia</v>
       </c>
-      <c r="Y5" s="82" t="str">
+      <c r="Y5" s="77" t="str">
         <f>IF(AI3="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="Z5" s="82"/>
+      <c r="Z5" s="77"/>
       <c r="AA5" s="37" t="str">
         <v>Bosnia</v>
       </c>
@@ -2941,11 +2941,11 @@
       <c r="AJ5" s="9"/>
     </row>
     <row r="6" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="82" t="str">
+      <c r="A6" s="77" t="str">
         <f>IF(K3="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="B6" s="82"/>
+      <c r="B6" s="77"/>
       <c r="C6" s="33" t="str">
         <v>South Korea</v>
       </c>
@@ -3000,11 +3000,11 @@
         <f>B_Team3</f>
         <v>Qatar</v>
       </c>
-      <c r="Y6" s="82" t="str">
+      <c r="Y6" s="77" t="str">
         <f>IF(AI3="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="Z6" s="82"/>
+      <c r="Z6" s="77"/>
       <c r="AA6" s="37" t="str">
         <v>Qatar</v>
       </c>
@@ -3033,11 +3033,11 @@
       <c r="AJ6" s="9"/>
     </row>
     <row r="7" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="82" t="str">
+      <c r="A7" s="77" t="str">
         <f>IF(K3="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="B7" s="82"/>
+      <c r="B7" s="77"/>
       <c r="C7" s="42" t="str">
         <v>Czechia</v>
       </c>
@@ -3092,11 +3092,11 @@
         <f>B_Team1</f>
         <v>Canada</v>
       </c>
-      <c r="Y7" s="82" t="str">
+      <c r="Y7" s="77" t="str">
         <f>IF(AI3="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="Z7" s="82"/>
+      <c r="Z7" s="77"/>
       <c r="AA7" s="46" t="str">
         <v>Switzerland</v>
       </c>
@@ -3235,22 +3235,22 @@
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="4"/>
-      <c r="M10" s="83" t="s">
+      <c r="M10" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="N10" s="83"/>
-      <c r="O10" s="83"/>
-      <c r="P10" s="83"/>
-      <c r="Q10" s="83"/>
+      <c r="N10" s="78"/>
+      <c r="O10" s="78"/>
+      <c r="P10" s="78"/>
+      <c r="Q10" s="78"/>
       <c r="R10" s="59"/>
       <c r="S10" s="14"/>
-      <c r="T10" s="84" t="s">
+      <c r="T10" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="U10" s="84"/>
-      <c r="V10" s="84"/>
-      <c r="W10" s="84"/>
-      <c r="X10" s="84"/>
+      <c r="U10" s="79"/>
+      <c r="V10" s="79"/>
+      <c r="W10" s="79"/>
+      <c r="X10" s="79"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="2"/>
       <c r="AA10" s="3"/>
@@ -3267,16 +3267,16 @@
     <row r="11" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="8"/>
-      <c r="C11" s="85" t="s">
+      <c r="C11" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="85"/>
-      <c r="J11" s="85"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80"/>
       <c r="K11" s="8"/>
       <c r="L11" s="9"/>
       <c r="M11" s="60"/>
@@ -3293,16 +3293,16 @@
       <c r="X11" s="16"/>
       <c r="Y11" s="7"/>
       <c r="Z11" s="8"/>
-      <c r="AA11" s="85" t="s">
+      <c r="AA11" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="AB11" s="85"/>
-      <c r="AC11" s="85"/>
-      <c r="AD11" s="85"/>
-      <c r="AE11" s="85"/>
-      <c r="AF11" s="85"/>
-      <c r="AG11" s="85"/>
-      <c r="AH11" s="85"/>
+      <c r="AB11" s="80"/>
+      <c r="AC11" s="80"/>
+      <c r="AD11" s="80"/>
+      <c r="AE11" s="80"/>
+      <c r="AF11" s="80"/>
+      <c r="AG11" s="80"/>
+      <c r="AH11" s="80"/>
       <c r="AI11" s="8"/>
       <c r="AJ11" s="9"/>
     </row>
@@ -3399,11 +3399,11 @@
       <c r="AJ12" s="9"/>
     </row>
     <row r="13" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="82" t="str">
+      <c r="A13" s="77" t="str">
         <f>IF(K12="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="B13" s="82"/>
+      <c r="B13" s="77"/>
       <c r="C13" s="33" t="str" cm="1">
         <f t="array" ref="C13:J16">_xlfn._xlws.SORT(C65:J68,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Brazil</v>
@@ -3459,11 +3459,11 @@
         <f>D_Team4</f>
         <v>Turkey</v>
       </c>
-      <c r="Y13" s="82" t="str">
+      <c r="Y13" s="77" t="str">
         <f>IF(AI12="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="Z13" s="82"/>
+      <c r="Z13" s="77"/>
       <c r="AA13" s="37" t="str" cm="1">
         <f t="array" ref="AA13:AH16">_xlfn._xlws.SORT(AA65:AH68,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>USA</v>
@@ -3493,11 +3493,11 @@
       <c r="AJ13" s="9"/>
     </row>
     <row r="14" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="82" t="str">
+      <c r="A14" s="77" t="str">
         <f>IF(K12="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="B14" s="82"/>
+      <c r="B14" s="77"/>
       <c r="C14" s="33" t="str">
         <v>Morocco</v>
       </c>
@@ -3552,11 +3552,11 @@
         <f>D_Team2</f>
         <v>Paraguay</v>
       </c>
-      <c r="Y14" s="82" t="str">
+      <c r="Y14" s="77" t="str">
         <f>IF(AI12="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="Z14" s="82"/>
+      <c r="Z14" s="77"/>
       <c r="AA14" s="37" t="str">
         <v>Paraguay</v>
       </c>
@@ -3585,11 +3585,11 @@
       <c r="AJ14" s="9"/>
     </row>
     <row r="15" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="82" t="str">
+      <c r="A15" s="77" t="str">
         <f>IF(K12="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="B15" s="82"/>
+      <c r="B15" s="77"/>
       <c r="C15" s="33" t="str">
         <v>Haiti</v>
       </c>
@@ -3644,11 +3644,11 @@
         <f>D_Team3</f>
         <v>Australia</v>
       </c>
-      <c r="Y15" s="82" t="str">
+      <c r="Y15" s="77" t="str">
         <f>IF(AI12="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="Z15" s="82"/>
+      <c r="Z15" s="77"/>
       <c r="AA15" s="37" t="str">
         <v>Australia</v>
       </c>
@@ -3677,11 +3677,11 @@
       <c r="AJ15" s="9"/>
     </row>
     <row r="16" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="82" t="str">
+      <c r="A16" s="77" t="str">
         <f>IF(K12="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="B16" s="82"/>
+      <c r="B16" s="77"/>
       <c r="C16" s="42" t="str">
         <v>Scotland</v>
       </c>
@@ -3736,11 +3736,11 @@
         <f>D_Team1</f>
         <v>USA</v>
       </c>
-      <c r="Y16" s="82" t="str">
+      <c r="Y16" s="77" t="str">
         <f>IF(AI12="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="Z16" s="82"/>
+      <c r="Z16" s="77"/>
       <c r="AA16" s="46" t="str">
         <v>Turkey</v>
       </c>
@@ -3879,22 +3879,22 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="4"/>
-      <c r="M19" s="83" t="s">
+      <c r="M19" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="N19" s="83"/>
-      <c r="O19" s="83"/>
-      <c r="P19" s="83"/>
-      <c r="Q19" s="83"/>
+      <c r="N19" s="78"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="78"/>
+      <c r="Q19" s="78"/>
       <c r="R19" s="59"/>
       <c r="S19" s="14"/>
-      <c r="T19" s="84" t="s">
+      <c r="T19" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="U19" s="84"/>
-      <c r="V19" s="84"/>
-      <c r="W19" s="84"/>
-      <c r="X19" s="84"/>
+      <c r="U19" s="79"/>
+      <c r="V19" s="79"/>
+      <c r="W19" s="79"/>
+      <c r="X19" s="79"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="2"/>
       <c r="AA19" s="3"/>
@@ -3911,16 +3911,16 @@
     <row r="20" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="8"/>
-      <c r="C20" s="85" t="s">
+      <c r="C20" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="85"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="85"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="85"/>
-      <c r="J20" s="85"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="80"/>
       <c r="K20" s="8"/>
       <c r="L20" s="9"/>
       <c r="M20" s="60"/>
@@ -3937,16 +3937,16 @@
       <c r="X20" s="16"/>
       <c r="Y20" s="7"/>
       <c r="Z20" s="8"/>
-      <c r="AA20" s="85" t="s">
+      <c r="AA20" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="AB20" s="85"/>
-      <c r="AC20" s="85"/>
-      <c r="AD20" s="85"/>
-      <c r="AE20" s="85"/>
-      <c r="AF20" s="85"/>
-      <c r="AG20" s="85"/>
-      <c r="AH20" s="85"/>
+      <c r="AB20" s="80"/>
+      <c r="AC20" s="80"/>
+      <c r="AD20" s="80"/>
+      <c r="AE20" s="80"/>
+      <c r="AF20" s="80"/>
+      <c r="AG20" s="80"/>
+      <c r="AH20" s="80"/>
       <c r="AI20" s="8"/>
       <c r="AJ20" s="9"/>
     </row>
@@ -4043,11 +4043,11 @@
       <c r="AJ21" s="9"/>
     </row>
     <row r="22" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="82" t="str">
+      <c r="A22" s="77" t="str">
         <f>IF(K21="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="B22" s="82"/>
+      <c r="B22" s="77"/>
       <c r="C22" s="33" t="str" cm="1">
         <f t="array" ref="C22:J25">_xlfn._xlws.SORT(C72:J75,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Germany</v>
@@ -4103,11 +4103,11 @@
         <f>F_Team4</f>
         <v>Tunisia</v>
       </c>
-      <c r="Y22" s="82" t="str">
+      <c r="Y22" s="77" t="str">
         <f>IF(AI21="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="Z22" s="82"/>
+      <c r="Z22" s="77"/>
       <c r="AA22" s="37" t="str" cm="1">
         <f t="array" ref="AA22:AH25">_xlfn._xlws.SORT(AA72:AH75,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Netherlands</v>
@@ -4137,11 +4137,11 @@
       <c r="AJ22" s="9"/>
     </row>
     <row r="23" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="82" t="str">
+      <c r="A23" s="77" t="str">
         <f>IF(K21="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="B23" s="82"/>
+      <c r="B23" s="77"/>
       <c r="C23" s="37" t="str">
         <v>Curacao</v>
       </c>
@@ -4196,11 +4196,11 @@
         <f>F_Team3</f>
         <v>Sweden</v>
       </c>
-      <c r="Y23" s="82" t="str">
+      <c r="Y23" s="77" t="str">
         <f>IF(AI21="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="Z23" s="82"/>
+      <c r="Z23" s="77"/>
       <c r="AA23" s="37" t="str">
         <v>Japan</v>
       </c>
@@ -4229,11 +4229,11 @@
       <c r="AJ23" s="9"/>
     </row>
     <row r="24" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="82" t="str">
+      <c r="A24" s="77" t="str">
         <f>IF(K21="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="B24" s="82"/>
+      <c r="B24" s="77"/>
       <c r="C24" s="37" t="str">
         <v>Ivory Coast</v>
       </c>
@@ -4288,11 +4288,11 @@
         <f>F_Team2</f>
         <v>Japan</v>
       </c>
-      <c r="Y24" s="82" t="str">
+      <c r="Y24" s="77" t="str">
         <f>IF(AI21="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="Z24" s="82"/>
+      <c r="Z24" s="77"/>
       <c r="AA24" s="37" t="str">
         <v>Sweden</v>
       </c>
@@ -4321,11 +4321,11 @@
       <c r="AJ24" s="9"/>
     </row>
     <row r="25" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="82" t="str">
+      <c r="A25" s="77" t="str">
         <f>IF(K21="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="B25" s="82"/>
+      <c r="B25" s="77"/>
       <c r="C25" s="46" t="str">
         <v>Ecuador</v>
       </c>
@@ -4380,11 +4380,11 @@
         <f>F_Team3</f>
         <v>Sweden</v>
       </c>
-      <c r="Y25" s="82" t="str">
+      <c r="Y25" s="77" t="str">
         <f>IF(AI21="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="Z25" s="82"/>
+      <c r="Z25" s="77"/>
       <c r="AA25" s="46" t="str">
         <v>Tunisia</v>
       </c>
@@ -4523,22 +4523,22 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="4"/>
-      <c r="M28" s="83" t="s">
+      <c r="M28" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="N28" s="83"/>
-      <c r="O28" s="83"/>
-      <c r="P28" s="83"/>
-      <c r="Q28" s="83"/>
+      <c r="N28" s="78"/>
+      <c r="O28" s="78"/>
+      <c r="P28" s="78"/>
+      <c r="Q28" s="78"/>
       <c r="R28" s="59"/>
       <c r="S28" s="14"/>
-      <c r="T28" s="84" t="s">
+      <c r="T28" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="U28" s="84"/>
-      <c r="V28" s="84"/>
-      <c r="W28" s="84"/>
-      <c r="X28" s="84"/>
+      <c r="U28" s="79"/>
+      <c r="V28" s="79"/>
+      <c r="W28" s="79"/>
+      <c r="X28" s="79"/>
       <c r="Y28" s="1"/>
       <c r="Z28" s="2"/>
       <c r="AA28" s="3"/>
@@ -4555,16 +4555,16 @@
     <row r="29" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7"/>
       <c r="B29" s="8"/>
-      <c r="C29" s="85" t="s">
+      <c r="C29" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="85"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="85"/>
-      <c r="J29" s="85"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="80"/>
+      <c r="G29" s="80"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
       <c r="K29" s="8"/>
       <c r="L29" s="9"/>
       <c r="M29" s="60"/>
@@ -4581,16 +4581,16 @@
       <c r="X29" s="16"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="8"/>
-      <c r="AA29" s="85" t="s">
+      <c r="AA29" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="AB29" s="85"/>
-      <c r="AC29" s="85"/>
-      <c r="AD29" s="85"/>
-      <c r="AE29" s="85"/>
-      <c r="AF29" s="85"/>
-      <c r="AG29" s="85"/>
-      <c r="AH29" s="85"/>
+      <c r="AB29" s="80"/>
+      <c r="AC29" s="80"/>
+      <c r="AD29" s="80"/>
+      <c r="AE29" s="80"/>
+      <c r="AF29" s="80"/>
+      <c r="AG29" s="80"/>
+      <c r="AH29" s="80"/>
       <c r="AI29" s="8"/>
       <c r="AJ29" s="9"/>
     </row>
@@ -4687,11 +4687,11 @@
       <c r="AJ30" s="9"/>
     </row>
     <row r="31" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="82" t="str">
+      <c r="A31" s="77" t="str">
         <f>IF(K30="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="B31" s="82"/>
+      <c r="B31" s="77"/>
       <c r="C31" s="33" t="str" cm="1">
         <f t="array" ref="C31:J34">_xlfn._xlws.SORT(C79:J82,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Belgium</v>
@@ -4747,11 +4747,11 @@
         <f>H_Team2</f>
         <v>Cabo Verde</v>
       </c>
-      <c r="Y31" s="82" t="str">
+      <c r="Y31" s="77" t="str">
         <f>IF(AI30="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="Z31" s="82"/>
+      <c r="Z31" s="77"/>
       <c r="AA31" s="37" t="str" cm="1">
         <f t="array" ref="AA31:AH34">_xlfn._xlws.SORT(AA79:AH82,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Spain</v>
@@ -4781,11 +4781,11 @@
       <c r="AJ31" s="9"/>
     </row>
     <row r="32" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="82" t="str">
+      <c r="A32" s="77" t="str">
         <f>IF(K30="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="B32" s="82"/>
+      <c r="B32" s="77"/>
       <c r="C32" s="37" t="str">
         <v>Egypt</v>
       </c>
@@ -4840,11 +4840,11 @@
         <f>H_Team2</f>
         <v>Cabo Verde</v>
       </c>
-      <c r="Y32" s="82" t="str">
+      <c r="Y32" s="77" t="str">
         <f>IF(AI30="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="Z32" s="82"/>
+      <c r="Z32" s="77"/>
       <c r="AA32" s="37" t="str">
         <v>Cabo Verde</v>
       </c>
@@ -4873,11 +4873,11 @@
       <c r="AJ32" s="9"/>
     </row>
     <row r="33" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="82" t="str">
+      <c r="A33" s="77" t="str">
         <f>IF(K30="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="B33" s="82"/>
+      <c r="B33" s="77"/>
       <c r="C33" s="37" t="str">
         <v>Iran</v>
       </c>
@@ -4932,11 +4932,11 @@
         <f>H_Team3</f>
         <v>Saudi Arabia</v>
       </c>
-      <c r="Y33" s="82" t="str">
+      <c r="Y33" s="77" t="str">
         <f>IF(AI30="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="Z33" s="82"/>
+      <c r="Z33" s="77"/>
       <c r="AA33" s="37" t="str">
         <v>Saudi Arabia</v>
       </c>
@@ -4965,11 +4965,11 @@
       <c r="AJ33" s="9"/>
     </row>
     <row r="34" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="82" t="str">
+      <c r="A34" s="77" t="str">
         <f>IF(K30="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="B34" s="82"/>
+      <c r="B34" s="77"/>
       <c r="C34" s="46" t="str">
         <v>New Zealand</v>
       </c>
@@ -5024,11 +5024,11 @@
         <f>H_Team3</f>
         <v>Saudi Arabia</v>
       </c>
-      <c r="Y34" s="82" t="str">
+      <c r="Y34" s="77" t="str">
         <f>IF(AI30="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="Z34" s="82"/>
+      <c r="Z34" s="77"/>
       <c r="AA34" s="46" t="str">
         <v>Uruguay</v>
       </c>
@@ -5167,22 +5167,22 @@
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="4"/>
-      <c r="M37" s="83" t="s">
+      <c r="M37" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="N37" s="83"/>
-      <c r="O37" s="83"/>
-      <c r="P37" s="83"/>
-      <c r="Q37" s="83"/>
+      <c r="N37" s="78"/>
+      <c r="O37" s="78"/>
+      <c r="P37" s="78"/>
+      <c r="Q37" s="78"/>
       <c r="R37" s="59"/>
       <c r="S37" s="14"/>
-      <c r="T37" s="84" t="s">
+      <c r="T37" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="U37" s="84"/>
-      <c r="V37" s="84"/>
-      <c r="W37" s="84"/>
-      <c r="X37" s="84"/>
+      <c r="U37" s="79"/>
+      <c r="V37" s="79"/>
+      <c r="W37" s="79"/>
+      <c r="X37" s="79"/>
       <c r="Y37" s="1"/>
       <c r="Z37" s="2"/>
       <c r="AA37" s="3"/>
@@ -5199,16 +5199,16 @@
     <row r="38" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7"/>
       <c r="B38" s="8"/>
-      <c r="C38" s="85" t="s">
+      <c r="C38" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="D38" s="85"/>
-      <c r="E38" s="85"/>
-      <c r="F38" s="85"/>
-      <c r="G38" s="85"/>
-      <c r="H38" s="85"/>
-      <c r="I38" s="85"/>
-      <c r="J38" s="85"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="80"/>
+      <c r="G38" s="80"/>
+      <c r="H38" s="80"/>
+      <c r="I38" s="80"/>
+      <c r="J38" s="80"/>
       <c r="K38" s="8"/>
       <c r="L38" s="9"/>
       <c r="M38" s="60"/>
@@ -5225,16 +5225,16 @@
       <c r="X38" s="16"/>
       <c r="Y38" s="7"/>
       <c r="Z38" s="8"/>
-      <c r="AA38" s="85" t="s">
+      <c r="AA38" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="AB38" s="85"/>
-      <c r="AC38" s="85"/>
-      <c r="AD38" s="85"/>
-      <c r="AE38" s="85"/>
-      <c r="AF38" s="85"/>
-      <c r="AG38" s="85"/>
-      <c r="AH38" s="85"/>
+      <c r="AB38" s="80"/>
+      <c r="AC38" s="80"/>
+      <c r="AD38" s="80"/>
+      <c r="AE38" s="80"/>
+      <c r="AF38" s="80"/>
+      <c r="AG38" s="80"/>
+      <c r="AH38" s="80"/>
       <c r="AI38" s="8"/>
       <c r="AJ38" s="9"/>
     </row>
@@ -5331,11 +5331,11 @@
       <c r="AJ39" s="9"/>
     </row>
     <row r="40" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="82" t="str">
+      <c r="A40" s="77" t="str">
         <f>IF(K39="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="B40" s="82"/>
+      <c r="B40" s="77"/>
       <c r="C40" s="33" t="str" cm="1">
         <f t="array" ref="C40:J43">_xlfn._xlws.SORT(C86:J89,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>France</v>
@@ -5391,11 +5391,11 @@
         <f>J_Team4</f>
         <v>Jordan</v>
       </c>
-      <c r="Y40" s="82" t="str">
+      <c r="Y40" s="77" t="str">
         <f>IF(AI39="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="Z40" s="82"/>
+      <c r="Z40" s="77"/>
       <c r="AA40" s="37" t="str" cm="1">
         <f t="array" ref="AA40:AH43">_xlfn._xlws.SORT(AA86:AH89,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Argentina</v>
@@ -5425,11 +5425,11 @@
       <c r="AJ40" s="9"/>
     </row>
     <row r="41" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="82" t="str">
+      <c r="A41" s="77" t="str">
         <f>IF(K39="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="B41" s="82"/>
+      <c r="B41" s="77"/>
       <c r="C41" s="37" t="str">
         <v>Senegal</v>
       </c>
@@ -5484,11 +5484,11 @@
         <f>J_Team3</f>
         <v>Austria</v>
       </c>
-      <c r="Y41" s="82" t="str">
+      <c r="Y41" s="77" t="str">
         <f>IF(AI39="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="Z41" s="82"/>
+      <c r="Z41" s="77"/>
       <c r="AA41" s="37" t="str">
         <v>Algeria</v>
       </c>
@@ -5517,11 +5517,11 @@
       <c r="AJ41" s="9"/>
     </row>
     <row r="42" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="82" t="str">
+      <c r="A42" s="77" t="str">
         <f>IF(K39="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="B42" s="82"/>
+      <c r="B42" s="77"/>
       <c r="C42" s="37" t="str">
         <v>Iraq</v>
       </c>
@@ -5576,11 +5576,11 @@
         <f>J_Team2</f>
         <v>Algeria</v>
       </c>
-      <c r="Y42" s="82" t="str">
+      <c r="Y42" s="77" t="str">
         <f>IF(AI39="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="Z42" s="82"/>
+      <c r="Z42" s="77"/>
       <c r="AA42" s="37" t="str">
         <v>Austria</v>
       </c>
@@ -5609,11 +5609,11 @@
       <c r="AJ42" s="9"/>
     </row>
     <row r="43" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="82" t="str">
+      <c r="A43" s="77" t="str">
         <f>IF(K39="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="B43" s="82"/>
+      <c r="B43" s="77"/>
       <c r="C43" s="46" t="str">
         <v>Norway</v>
       </c>
@@ -5668,11 +5668,11 @@
         <f>J_Team3</f>
         <v>Austria</v>
       </c>
-      <c r="Y43" s="82" t="str">
+      <c r="Y43" s="77" t="str">
         <f>IF(AI39="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="Z43" s="82"/>
+      <c r="Z43" s="77"/>
       <c r="AA43" s="46" t="str">
         <v>Jordan</v>
       </c>
@@ -5811,22 +5811,22 @@
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="4"/>
-      <c r="M46" s="83" t="s">
+      <c r="M46" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="N46" s="83"/>
-      <c r="O46" s="83"/>
-      <c r="P46" s="83"/>
-      <c r="Q46" s="83"/>
+      <c r="N46" s="78"/>
+      <c r="O46" s="78"/>
+      <c r="P46" s="78"/>
+      <c r="Q46" s="78"/>
       <c r="R46" s="59"/>
       <c r="S46" s="14"/>
-      <c r="T46" s="84" t="s">
+      <c r="T46" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="U46" s="84"/>
-      <c r="V46" s="84"/>
-      <c r="W46" s="84"/>
-      <c r="X46" s="84"/>
+      <c r="U46" s="79"/>
+      <c r="V46" s="79"/>
+      <c r="W46" s="79"/>
+      <c r="X46" s="79"/>
       <c r="Y46" s="1"/>
       <c r="Z46" s="2"/>
       <c r="AA46" s="3"/>
@@ -5843,16 +5843,16 @@
     <row r="47" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7"/>
       <c r="B47" s="8"/>
-      <c r="C47" s="85" t="s">
+      <c r="C47" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="D47" s="85"/>
-      <c r="E47" s="85"/>
-      <c r="F47" s="85"/>
-      <c r="G47" s="85"/>
-      <c r="H47" s="85"/>
-      <c r="I47" s="85"/>
-      <c r="J47" s="85"/>
+      <c r="D47" s="80"/>
+      <c r="E47" s="80"/>
+      <c r="F47" s="80"/>
+      <c r="G47" s="80"/>
+      <c r="H47" s="80"/>
+      <c r="I47" s="80"/>
+      <c r="J47" s="80"/>
       <c r="K47" s="8"/>
       <c r="L47" s="9"/>
       <c r="M47" s="60"/>
@@ -5869,16 +5869,16 @@
       <c r="X47" s="16"/>
       <c r="Y47" s="7"/>
       <c r="Z47" s="8"/>
-      <c r="AA47" s="85" t="s">
+      <c r="AA47" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="AB47" s="85"/>
-      <c r="AC47" s="85"/>
-      <c r="AD47" s="85"/>
-      <c r="AE47" s="85"/>
-      <c r="AF47" s="85"/>
-      <c r="AG47" s="85"/>
-      <c r="AH47" s="85"/>
+      <c r="AB47" s="80"/>
+      <c r="AC47" s="80"/>
+      <c r="AD47" s="80"/>
+      <c r="AE47" s="80"/>
+      <c r="AF47" s="80"/>
+      <c r="AG47" s="80"/>
+      <c r="AH47" s="80"/>
       <c r="AI47" s="8"/>
       <c r="AJ47" s="9"/>
     </row>
@@ -5975,11 +5975,11 @@
       <c r="AJ48" s="9"/>
     </row>
     <row r="49" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="82" t="str">
+      <c r="A49" s="77" t="str">
         <f>IF(K48="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="B49" s="82"/>
+      <c r="B49" s="77"/>
       <c r="C49" s="33" t="str" cm="1">
         <f t="array" ref="C49:J52">_xlfn._xlws.SORT(C93:J96,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>Portugal</v>
@@ -6035,11 +6035,11 @@
         <f>L_Team2</f>
         <v>Croatia</v>
       </c>
-      <c r="Y49" s="82" t="str">
+      <c r="Y49" s="77" t="str">
         <f>IF(AI48="GROUP COMPLETE","1st","")</f>
         <v/>
       </c>
-      <c r="Z49" s="82"/>
+      <c r="Z49" s="77"/>
       <c r="AA49" s="37" t="str" cm="1">
         <f t="array" ref="AA49:AH52">_xlfn._xlws.SORT(AA93:AH96,{8,7,5},{-1,-1,-1},FALSE)</f>
         <v>England</v>
@@ -6069,11 +6069,11 @@
       <c r="AJ49" s="9"/>
     </row>
     <row r="50" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="82" t="str">
+      <c r="A50" s="77" t="str">
         <f>IF(K48="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="B50" s="82"/>
+      <c r="B50" s="77"/>
       <c r="C50" s="37" t="str">
         <v>Congo</v>
       </c>
@@ -6128,11 +6128,11 @@
         <f>L_Team3</f>
         <v>Ghana</v>
       </c>
-      <c r="Y50" s="82" t="str">
+      <c r="Y50" s="77" t="str">
         <f>IF(AI48="GROUP COMPLETE","2nd","")</f>
         <v/>
       </c>
-      <c r="Z50" s="82"/>
+      <c r="Z50" s="77"/>
       <c r="AA50" s="37" t="str">
         <v>Croatia</v>
       </c>
@@ -6161,11 +6161,11 @@
       <c r="AJ50" s="9"/>
     </row>
     <row r="51" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="82" t="str">
+      <c r="A51" s="77" t="str">
         <f>IF(K48="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="B51" s="82"/>
+      <c r="B51" s="77"/>
       <c r="C51" s="37" t="str">
         <v>Uzbekistan</v>
       </c>
@@ -6220,11 +6220,11 @@
         <f>L_Team2</f>
         <v>Croatia</v>
       </c>
-      <c r="Y51" s="82" t="str">
+      <c r="Y51" s="77" t="str">
         <f>IF(AI48="GROUP COMPLETE","3rd","")</f>
         <v/>
       </c>
-      <c r="Z51" s="82"/>
+      <c r="Z51" s="77"/>
       <c r="AA51" s="37" t="str">
         <v>Ghana</v>
       </c>
@@ -6253,11 +6253,11 @@
       <c r="AJ51" s="9"/>
     </row>
     <row r="52" spans="1:36" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="82" t="str">
+      <c r="A52" s="77" t="str">
         <f>IF(K48="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="B52" s="82"/>
+      <c r="B52" s="77"/>
       <c r="C52" s="46" t="str">
         <v>Colombia</v>
       </c>
@@ -6312,11 +6312,11 @@
         <f>L_Team1</f>
         <v>England</v>
       </c>
-      <c r="Y52" s="82" t="str">
+      <c r="Y52" s="77" t="str">
         <f>IF(AI48="GROUP COMPLETE","4th","")</f>
         <v/>
       </c>
-      <c r="Z52" s="82"/>
+      <c r="Z52" s="77"/>
       <c r="AA52" s="46" t="str">
         <v>Panama</v>
       </c>
@@ -6444,16 +6444,16 @@
     </row>
     <row r="56" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="75"/>
-      <c r="C56" s="87" t="s">
+      <c r="C56" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="D56" s="87"/>
-      <c r="E56" s="87"/>
-      <c r="F56" s="87"/>
-      <c r="G56" s="87"/>
-      <c r="H56" s="87"/>
-      <c r="I56" s="87"/>
-      <c r="J56" s="87"/>
+      <c r="D56" s="82"/>
+      <c r="E56" s="82"/>
+      <c r="F56" s="82"/>
+      <c r="G56" s="82"/>
+      <c r="H56" s="82"/>
+      <c r="I56" s="82"/>
+      <c r="J56" s="82"/>
       <c r="K56" s="75"/>
       <c r="L56" s="75"/>
       <c r="M56" s="75"/>
@@ -6470,16 +6470,16 @@
       <c r="X56" s="75"/>
       <c r="Y56" s="75"/>
       <c r="Z56" s="75"/>
-      <c r="AA56" s="87" t="s">
+      <c r="AA56" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="AB56" s="87"/>
-      <c r="AC56" s="87"/>
-      <c r="AD56" s="87"/>
-      <c r="AE56" s="87"/>
-      <c r="AF56" s="87"/>
-      <c r="AG56" s="87"/>
-      <c r="AH56" s="87"/>
+      <c r="AB56" s="82"/>
+      <c r="AC56" s="82"/>
+      <c r="AD56" s="82"/>
+      <c r="AE56" s="82"/>
+      <c r="AF56" s="82"/>
+      <c r="AG56" s="82"/>
+      <c r="AH56" s="82"/>
       <c r="AI56" s="75"/>
       <c r="AJ56" s="75"/>
     </row>
@@ -6685,7 +6685,7 @@
       <c r="Y59" s="75"/>
       <c r="Z59" s="75"/>
       <c r="AA59" s="75" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AB59" s="75" cm="1">
         <f t="array" ref="AB59">SUMPRODUCT((T$3:T$8=AA59)*(U$3:U$8&gt;W$3:W$8)) + SUMPRODUCT((X$3:X$8=AA59)*(W$3:W$8&gt;U$3:U$8))</f>
@@ -6804,7 +6804,7 @@
     <row r="61" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="75"/>
       <c r="C61" s="75" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D61" s="75" cm="1">
         <f t="array" ref="D61">SUMPRODUCT((M$3:M$8=C61)*(N$3:N$8&gt;P$3:P$8)) + SUMPRODUCT((Q$3:Q$8=C61)*(P$3:P$8&gt;N$3:N$8))</f>
@@ -6923,16 +6923,16 @@
     </row>
     <row r="63" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="75"/>
-      <c r="C63" s="87" t="s">
+      <c r="C63" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="D63" s="87"/>
-      <c r="E63" s="87"/>
-      <c r="F63" s="87"/>
-      <c r="G63" s="87"/>
-      <c r="H63" s="87"/>
-      <c r="I63" s="87"/>
-      <c r="J63" s="87"/>
+      <c r="D63" s="82"/>
+      <c r="E63" s="82"/>
+      <c r="F63" s="82"/>
+      <c r="G63" s="82"/>
+      <c r="H63" s="82"/>
+      <c r="I63" s="82"/>
+      <c r="J63" s="82"/>
       <c r="K63" s="75"/>
       <c r="L63" s="75"/>
       <c r="M63" s="75"/>
@@ -6949,16 +6949,16 @@
       <c r="X63" s="75"/>
       <c r="Y63" s="75"/>
       <c r="Z63" s="75"/>
-      <c r="AA63" s="87" t="s">
+      <c r="AA63" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="AB63" s="87"/>
-      <c r="AC63" s="87"/>
-      <c r="AD63" s="87"/>
-      <c r="AE63" s="87"/>
-      <c r="AF63" s="87"/>
-      <c r="AG63" s="87"/>
-      <c r="AH63" s="87"/>
+      <c r="AB63" s="82"/>
+      <c r="AC63" s="82"/>
+      <c r="AD63" s="82"/>
+      <c r="AE63" s="82"/>
+      <c r="AF63" s="82"/>
+      <c r="AG63" s="82"/>
+      <c r="AH63" s="82"/>
       <c r="AI63" s="75"/>
       <c r="AJ63" s="75"/>
     </row>
@@ -7402,16 +7402,16 @@
     </row>
     <row r="70" spans="2:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="75"/>
-      <c r="C70" s="87" t="s">
+      <c r="C70" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="D70" s="87"/>
-      <c r="E70" s="87"/>
-      <c r="F70" s="87"/>
-      <c r="G70" s="87"/>
-      <c r="H70" s="87"/>
-      <c r="I70" s="87"/>
-      <c r="J70" s="87"/>
+      <c r="D70" s="82"/>
+      <c r="E70" s="82"/>
+      <c r="F70" s="82"/>
+      <c r="G70" s="82"/>
+      <c r="H70" s="82"/>
+      <c r="I70" s="82"/>
+      <c r="J70" s="82"/>
       <c r="K70" s="75"/>
       <c r="L70" s="75"/>
       <c r="M70" s="75"/>
@@ -7428,16 +7428,16 @@
       <c r="X70" s="75"/>
       <c r="Y70" s="75"/>
       <c r="Z70" s="75"/>
-      <c r="AA70" s="87" t="s">
+      <c r="AA70" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="AB70" s="87"/>
-      <c r="AC70" s="87"/>
-      <c r="AD70" s="87"/>
-      <c r="AE70" s="87"/>
-      <c r="AF70" s="87"/>
-      <c r="AG70" s="87"/>
-      <c r="AH70" s="87"/>
+      <c r="AB70" s="82"/>
+      <c r="AC70" s="82"/>
+      <c r="AD70" s="82"/>
+      <c r="AE70" s="82"/>
+      <c r="AF70" s="82"/>
+      <c r="AG70" s="82"/>
+      <c r="AH70" s="82"/>
       <c r="AI70" s="75"/>
       <c r="AJ70" s="75"/>
     </row>
@@ -7726,7 +7726,7 @@
       <c r="Y74" s="75"/>
       <c r="Z74" s="75"/>
       <c r="AA74" s="75" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AB74" s="75" cm="1">
         <f t="array" ref="AB74">SUMPRODUCT((T$21:T$26=AA74)*(U$21:U$26&gt;W$21:W$26)) + SUMPRODUCT((X$21:X$26=AA74)*(W$21:W$26&gt;U$21:U$26))</f>
@@ -7881,16 +7881,16 @@
     </row>
     <row r="77" spans="2:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="75"/>
-      <c r="C77" s="87" t="s">
+      <c r="C77" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="D77" s="87"/>
-      <c r="E77" s="87"/>
-      <c r="F77" s="87"/>
-      <c r="G77" s="87"/>
-      <c r="H77" s="87"/>
-      <c r="I77" s="87"/>
-      <c r="J77" s="87"/>
+      <c r="D77" s="82"/>
+      <c r="E77" s="82"/>
+      <c r="F77" s="82"/>
+      <c r="G77" s="82"/>
+      <c r="H77" s="82"/>
+      <c r="I77" s="82"/>
+      <c r="J77" s="82"/>
       <c r="K77" s="75"/>
       <c r="L77" s="75"/>
       <c r="M77" s="75"/>
@@ -7907,16 +7907,16 @@
       <c r="X77" s="75"/>
       <c r="Y77" s="75"/>
       <c r="Z77" s="75"/>
-      <c r="AA77" s="87" t="s">
+      <c r="AA77" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="AB77" s="87"/>
-      <c r="AC77" s="87"/>
-      <c r="AD77" s="87"/>
-      <c r="AE77" s="87"/>
-      <c r="AF77" s="87"/>
-      <c r="AG77" s="87"/>
-      <c r="AH77" s="87"/>
+      <c r="AB77" s="82"/>
+      <c r="AC77" s="82"/>
+      <c r="AD77" s="82"/>
+      <c r="AE77" s="82"/>
+      <c r="AF77" s="82"/>
+      <c r="AG77" s="82"/>
+      <c r="AH77" s="82"/>
       <c r="AI77" s="75"/>
       <c r="AJ77" s="75"/>
     </row>
@@ -8360,16 +8360,16 @@
     </row>
     <row r="84" spans="2:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="75"/>
-      <c r="C84" s="87" t="s">
+      <c r="C84" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="D84" s="87"/>
-      <c r="E84" s="87"/>
-      <c r="F84" s="87"/>
-      <c r="G84" s="87"/>
-      <c r="H84" s="87"/>
-      <c r="I84" s="87"/>
-      <c r="J84" s="87"/>
+      <c r="D84" s="82"/>
+      <c r="E84" s="82"/>
+      <c r="F84" s="82"/>
+      <c r="G84" s="82"/>
+      <c r="H84" s="82"/>
+      <c r="I84" s="82"/>
+      <c r="J84" s="82"/>
       <c r="K84" s="75"/>
       <c r="L84" s="75"/>
       <c r="M84" s="75"/>
@@ -8386,16 +8386,16 @@
       <c r="X84" s="75"/>
       <c r="Y84" s="75"/>
       <c r="Z84" s="75"/>
-      <c r="AA84" s="87" t="s">
+      <c r="AA84" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="AB84" s="87"/>
-      <c r="AC84" s="87"/>
-      <c r="AD84" s="87"/>
-      <c r="AE84" s="87"/>
-      <c r="AF84" s="87"/>
-      <c r="AG84" s="87"/>
-      <c r="AH84" s="87"/>
+      <c r="AB84" s="82"/>
+      <c r="AC84" s="82"/>
+      <c r="AD84" s="82"/>
+      <c r="AE84" s="82"/>
+      <c r="AF84" s="82"/>
+      <c r="AG84" s="82"/>
+      <c r="AH84" s="82"/>
       <c r="AI84" s="75"/>
       <c r="AJ84" s="75"/>
     </row>
@@ -8637,7 +8637,7 @@
     <row r="88" spans="2:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="75"/>
       <c r="C88" s="75" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D88" s="75" cm="1">
         <f t="array" ref="D88">SUMPRODUCT((M$39:M$44=C88)*(N$39:N$44&gt;P$39:P$44)) + SUMPRODUCT((Q$39:Q$44=C88)*(P$39:P$44&gt;N$39:N$44))</f>
@@ -8839,16 +8839,16 @@
     </row>
     <row r="91" spans="2:36" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="75"/>
-      <c r="C91" s="87" t="s">
+      <c r="C91" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="D91" s="87"/>
-      <c r="E91" s="87"/>
-      <c r="F91" s="87"/>
-      <c r="G91" s="87"/>
-      <c r="H91" s="87"/>
-      <c r="I91" s="87"/>
-      <c r="J91" s="87"/>
+      <c r="D91" s="82"/>
+      <c r="E91" s="82"/>
+      <c r="F91" s="82"/>
+      <c r="G91" s="82"/>
+      <c r="H91" s="82"/>
+      <c r="I91" s="82"/>
+      <c r="J91" s="82"/>
       <c r="K91" s="75"/>
       <c r="L91" s="75"/>
       <c r="M91" s="75"/>
@@ -8865,16 +8865,16 @@
       <c r="X91" s="75"/>
       <c r="Y91" s="75"/>
       <c r="Z91" s="75"/>
-      <c r="AA91" s="87" t="s">
+      <c r="AA91" s="82" t="s">
         <v>84</v>
       </c>
-      <c r="AB91" s="87"/>
-      <c r="AC91" s="87"/>
-      <c r="AD91" s="87"/>
-      <c r="AE91" s="87"/>
-      <c r="AF91" s="87"/>
-      <c r="AG91" s="87"/>
-      <c r="AH91" s="87"/>
+      <c r="AB91" s="82"/>
+      <c r="AC91" s="82"/>
+      <c r="AD91" s="82"/>
+      <c r="AE91" s="82"/>
+      <c r="AF91" s="82"/>
+      <c r="AG91" s="82"/>
+      <c r="AH91" s="82"/>
       <c r="AI91" s="75"/>
       <c r="AJ91" s="75"/>
     </row>
@@ -11452,21 +11452,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="86" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="86"/>
     </row>
     <row r="2" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="72"/>
@@ -11479,12 +11479,12 @@
       <c r="H2" s="73"/>
       <c r="I2" s="73"/>
       <c r="J2" s="73"/>
-      <c r="K2" s="81" t="str">
+      <c r="K2" s="87" t="str">
         <f>"Completed ("&amp;SUM(20-SUM(COUNTIF(J4,"")+COUNTIF(J6,"")+COUNTIF(I8,"")+COUNTIF(I10,"")+COUNTIF(J12,"")+COUNTIF(K14,"")+COUNTIF(K16,"")+COUNTIF(G18,"")+COUNTIF(H20,"")+COUNTIF(K22,"")+COUNTIF(L24,"&lt;=0")+COUNTIF(I26,"")+COUNTIF(J28,"")+COUNTIF(I30,"")+COUNTIF(I32,"")+COUNTIF(H34,"")+COUNTIF(I36,"")+COUNTIF(I38,"")+COUNTIF(H40,"")+COUNTIF(H42,"")))&amp;" out of 20)"</f>
         <v>Completed (1 out of 20)</v>
       </c>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="64"/>
@@ -11513,9 +11513,9 @@
       <c r="G4" s="64"/>
       <c r="H4" s="64"/>
       <c r="I4" s="64"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="78"/>
-      <c r="L4" s="79"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="85"/>
       <c r="M4" s="64"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -11545,9 +11545,9 @@
       <c r="G6" s="64"/>
       <c r="H6" s="64"/>
       <c r="I6" s="64"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="78"/>
-      <c r="L6" s="79"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="84"/>
+      <c r="L6" s="85"/>
       <c r="M6" s="64"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -11576,9 +11576,9 @@
       <c r="F8" s="64"/>
       <c r="G8" s="64"/>
       <c r="H8" s="64"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="78"/>
-      <c r="K8" s="79"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="84"/>
+      <c r="K8" s="85"/>
       <c r="L8" s="64"/>
       <c r="M8" s="64"/>
     </row>
@@ -11608,9 +11608,9 @@
       <c r="F10" s="64"/>
       <c r="G10" s="64"/>
       <c r="H10" s="64"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="78"/>
-      <c r="K10" s="79"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="84"/>
+      <c r="K10" s="85"/>
       <c r="L10" s="64"/>
       <c r="M10" s="64"/>
     </row>
@@ -11674,9 +11674,9 @@
       <c r="H14" s="64"/>
       <c r="I14" s="64"/>
       <c r="J14" s="64"/>
-      <c r="K14" s="77"/>
-      <c r="L14" s="78"/>
-      <c r="M14" s="79"/>
+      <c r="K14" s="83"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="85"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="64"/>
@@ -11706,9 +11706,9 @@
       <c r="H16" s="64"/>
       <c r="I16" s="64"/>
       <c r="J16" s="64"/>
-      <c r="K16" s="77"/>
-      <c r="L16" s="78"/>
-      <c r="M16" s="79"/>
+      <c r="K16" s="83"/>
+      <c r="L16" s="84"/>
+      <c r="M16" s="85"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="64"/>
@@ -11802,9 +11802,9 @@
       <c r="H22" s="64"/>
       <c r="I22" s="64"/>
       <c r="J22" s="64"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="78"/>
-      <c r="M22" s="79"/>
+      <c r="K22" s="83"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="85"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="64"/>
@@ -11823,7 +11823,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="64" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B24" s="64"/>
       <c r="C24" s="64"/>
@@ -11900,8 +11900,8 @@
       <c r="G28" s="64"/>
       <c r="H28" s="64"/>
       <c r="I28" s="64"/>
-      <c r="J28" s="77"/>
-      <c r="K28" s="79"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="85"/>
       <c r="L28" s="64"/>
       <c r="M28" s="64"/>
     </row>
@@ -12027,9 +12027,9 @@
       <c r="F36" s="64"/>
       <c r="G36" s="64"/>
       <c r="H36" s="64"/>
-      <c r="I36" s="77"/>
-      <c r="J36" s="78"/>
-      <c r="K36" s="79"/>
+      <c r="I36" s="83"/>
+      <c r="J36" s="84"/>
+      <c r="K36" s="85"/>
       <c r="L36" s="64"/>
       <c r="M36" s="64"/>
     </row>
@@ -12059,10 +12059,10 @@
       <c r="F38" s="64"/>
       <c r="G38" s="64"/>
       <c r="H38" s="64"/>
-      <c r="I38" s="77"/>
-      <c r="J38" s="78"/>
-      <c r="K38" s="78"/>
-      <c r="L38" s="79"/>
+      <c r="I38" s="83"/>
+      <c r="J38" s="84"/>
+      <c r="K38" s="84"/>
+      <c r="L38" s="85"/>
       <c r="M38" s="64"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
@@ -12090,10 +12090,10 @@
       <c r="E40" s="64"/>
       <c r="F40" s="64"/>
       <c r="G40" s="64"/>
-      <c r="H40" s="77"/>
-      <c r="I40" s="78"/>
-      <c r="J40" s="78"/>
-      <c r="K40" s="79"/>
+      <c r="H40" s="83"/>
+      <c r="I40" s="84"/>
+      <c r="J40" s="84"/>
+      <c r="K40" s="85"/>
       <c r="L40" s="64"/>
       <c r="M40" s="64"/>
     </row>
@@ -12122,10 +12122,10 @@
       <c r="E42" s="64"/>
       <c r="F42" s="64"/>
       <c r="G42" s="64"/>
-      <c r="H42" s="77"/>
-      <c r="I42" s="78"/>
-      <c r="J42" s="78"/>
-      <c r="K42" s="79"/>
+      <c r="H42" s="83"/>
+      <c r="I42" s="84"/>
+      <c r="J42" s="84"/>
+      <c r="K42" s="85"/>
       <c r="L42" s="64"/>
       <c r="M42" s="64"/>
     </row>
@@ -12171,7 +12171,7 @@
       <c r="G47" s="67"/>
       <c r="H47" s="67"/>
       <c r="I47" s="67" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J47" s="67"/>
       <c r="K47" s="67"/>
@@ -12238,10 +12238,10 @@
         <v>Argentina</v>
       </c>
       <c r="H49" s="65" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="I49" s="65" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="J49" s="67"/>
       <c r="K49" s="67"/>
@@ -12272,10 +12272,10 @@
         <v>Australia</v>
       </c>
       <c r="H50" s="65" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I50" s="65" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J50" s="67"/>
       <c r="K50" s="67"/>
@@ -12572,10 +12572,10 @@
         <v>Croatia</v>
       </c>
       <c r="H59" s="65" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I59" s="65" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J59" s="67"/>
       <c r="K59" s="67"/>
@@ -12764,10 +12764,10 @@
         <v>France</v>
       </c>
       <c r="H65" s="65" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I65" s="65" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J65" s="67"/>
       <c r="K65" s="67"/>
@@ -12988,10 +12988,10 @@
         <v>Japan</v>
       </c>
       <c r="H72" s="68" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I72" s="68" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J72" s="67"/>
       <c r="K72" s="67"/>
@@ -13020,10 +13020,10 @@
         <v>Jordan</v>
       </c>
       <c r="H73" s="68" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I73" s="68" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J73" s="67"/>
       <c r="K73" s="67"/>
@@ -13084,10 +13084,10 @@
         <v>Mexico</v>
       </c>
       <c r="H75" s="68" t="s">
-        <v>146</v>
+        <v>201</v>
       </c>
       <c r="I75" s="68" t="s">
-        <v>146</v>
+        <v>201</v>
       </c>
       <c r="J75" s="67"/>
       <c r="K75" s="67"/>
@@ -13116,10 +13116,10 @@
         <v>Morocco</v>
       </c>
       <c r="H76" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I76" s="68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J76" s="67"/>
       <c r="K76" s="67"/>
@@ -13148,10 +13148,10 @@
         <v>Netherlands</v>
       </c>
       <c r="H77" s="68" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I77" s="68" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J77" s="67"/>
       <c r="K77" s="67"/>
@@ -13180,10 +13180,10 @@
         <v>New Zealand</v>
       </c>
       <c r="H78" s="68" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I78" s="68" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J78" s="67"/>
       <c r="K78" s="67"/>
@@ -13212,10 +13212,10 @@
         <v>Norway</v>
       </c>
       <c r="H79" s="68" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I79" s="68" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J79" s="67"/>
       <c r="K79" s="67"/>
@@ -13244,10 +13244,10 @@
         <v>Panama</v>
       </c>
       <c r="H80" s="68" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I80" s="68" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J80" s="67"/>
       <c r="K80" s="67"/>
@@ -13276,10 +13276,10 @@
         <v>Paraguay</v>
       </c>
       <c r="H81" s="68" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I81" s="68" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J81" s="67"/>
       <c r="K81" s="67"/>
@@ -13308,10 +13308,10 @@
         <v>Sweden</v>
       </c>
       <c r="H82" s="68" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I82" s="68" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J82" s="67"/>
       <c r="K82" s="67"/>
@@ -13340,10 +13340,10 @@
         <v>Portugal</v>
       </c>
       <c r="H83" s="68" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I83" s="68" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J83" s="67"/>
       <c r="K83" s="67"/>
@@ -13372,10 +13372,10 @@
         <v>Qatar</v>
       </c>
       <c r="H84" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I84" s="68" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J84" s="67"/>
       <c r="K84" s="67"/>
@@ -13404,10 +13404,10 @@
         <v>Saudi Arabia</v>
       </c>
       <c r="H85" s="68" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I85" s="68" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J85" s="67"/>
       <c r="K85" s="67"/>
@@ -13436,10 +13436,10 @@
         <v>Scotland</v>
       </c>
       <c r="H86" s="68" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I86" s="68" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J86" s="67"/>
       <c r="K86" s="67"/>
@@ -13468,10 +13468,10 @@
         <v>Senegal</v>
       </c>
       <c r="H87" s="68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I87" s="68" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J87" s="67"/>
       <c r="K87" s="67"/>
@@ -13500,10 +13500,10 @@
         <v>South Africa</v>
       </c>
       <c r="H88" s="68" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I88" s="68" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J88" s="67"/>
       <c r="K88" s="67"/>
@@ -13532,10 +13532,10 @@
         <v>Spain</v>
       </c>
       <c r="H89" s="68" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I89" s="68" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J89" s="67"/>
       <c r="K89" s="67"/>
@@ -13564,10 +13564,10 @@
         <v>Switzerland</v>
       </c>
       <c r="H90" s="68" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I90" s="68" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J90" s="67"/>
       <c r="K90" s="67"/>
@@ -13596,10 +13596,10 @@
         <v>Tunisia</v>
       </c>
       <c r="H91" s="68" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I91" s="68" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J91" s="67"/>
       <c r="K91" s="67"/>
@@ -13628,10 +13628,10 @@
         <v>Turkey</v>
       </c>
       <c r="H92" s="68" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I92" s="68" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J92" s="67"/>
       <c r="K92" s="67"/>
@@ -13660,10 +13660,10 @@
         <v>Uruguay</v>
       </c>
       <c r="H93" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I93" s="68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J93" s="67"/>
       <c r="K93" s="67"/>
@@ -13692,10 +13692,10 @@
         <v>USA</v>
       </c>
       <c r="H94" s="68" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I94" s="68" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J94" s="67"/>
       <c r="K94" s="67"/>
@@ -13724,10 +13724,10 @@
         <v>Uzbekistan</v>
       </c>
       <c r="H95" s="68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I95" s="68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J95" s="67"/>
       <c r="K95" s="67"/>
@@ -13741,10 +13741,10 @@
       <c r="F96" s="67"/>
       <c r="G96" s="67"/>
       <c r="H96" s="68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I96" s="68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J96" s="67"/>
       <c r="K96" s="67"/>
@@ -13758,10 +13758,10 @@
       <c r="F97" s="67"/>
       <c r="G97" s="67"/>
       <c r="H97" s="68" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I97" s="68" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J97" s="67"/>
       <c r="K97" s="67"/>
@@ -13775,10 +13775,10 @@
       <c r="F98" s="67"/>
       <c r="G98" s="67"/>
       <c r="H98" s="68" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I98" s="68" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J98" s="67"/>
       <c r="K98" s="67"/>
@@ -13792,10 +13792,10 @@
       <c r="F99" s="67"/>
       <c r="G99" s="67"/>
       <c r="H99" s="68" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I99" s="68" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J99" s="67"/>
       <c r="K99" s="67"/>
@@ -13809,10 +13809,10 @@
       <c r="F100" s="67"/>
       <c r="G100" s="67"/>
       <c r="H100" s="68" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I100" s="68" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J100" s="67"/>
       <c r="K100" s="67"/>
@@ -13826,10 +13826,10 @@
       <c r="F101" s="67"/>
       <c r="G101" s="67"/>
       <c r="H101" s="68" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="I101" s="68" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="J101" s="67"/>
       <c r="K101" s="67"/>
@@ -13843,10 +13843,10 @@
       <c r="F102" s="67"/>
       <c r="G102" s="67"/>
       <c r="H102" s="68" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I102" s="68" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J102" s="67"/>
       <c r="K102" s="67"/>
@@ -13860,10 +13860,10 @@
       <c r="F103" s="67"/>
       <c r="G103" s="67"/>
       <c r="H103" s="68" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I103" s="68" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J103" s="67"/>
       <c r="K103" s="67"/>
@@ -13877,10 +13877,10 @@
       <c r="F104" s="67"/>
       <c r="G104" s="67"/>
       <c r="H104" s="68" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I104" s="68" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J104" s="67"/>
       <c r="K104" s="67"/>
@@ -13894,10 +13894,10 @@
       <c r="F105" s="67"/>
       <c r="G105" s="67"/>
       <c r="H105" s="68" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I105" s="68" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J105" s="67"/>
       <c r="K105" s="67"/>
@@ -13911,10 +13911,10 @@
       <c r="F106" s="67"/>
       <c r="G106" s="67"/>
       <c r="H106" s="68" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I106" s="68" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J106" s="67"/>
       <c r="K106" s="67"/>
@@ -13928,10 +13928,10 @@
       <c r="F107" s="67"/>
       <c r="G107" s="67"/>
       <c r="H107" s="68" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I107" s="68" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J107" s="67"/>
       <c r="K107" s="67"/>
@@ -13945,10 +13945,10 @@
       <c r="F108" s="67"/>
       <c r="G108" s="67"/>
       <c r="H108" s="68" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I108" s="68" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J108" s="67"/>
       <c r="K108" s="67"/>
@@ -13962,10 +13962,10 @@
       <c r="F109" s="67"/>
       <c r="G109" s="67"/>
       <c r="H109" s="68" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I109" s="68" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="J109" s="67"/>
       <c r="K109" s="67"/>
@@ -13979,10 +13979,10 @@
       <c r="F110" s="67"/>
       <c r="G110" s="67"/>
       <c r="H110" s="68" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I110" s="68" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J110" s="67"/>
       <c r="K110" s="67"/>
@@ -13996,10 +13996,10 @@
       <c r="F111" s="67"/>
       <c r="G111" s="67"/>
       <c r="H111" s="68" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I111" s="68" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J111" s="67"/>
       <c r="K111" s="67"/>
@@ -14013,10 +14013,10 @@
       <c r="F112" s="67"/>
       <c r="G112" s="67"/>
       <c r="H112" s="68" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I112" s="68" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J112" s="67"/>
       <c r="K112" s="67"/>
@@ -14030,10 +14030,10 @@
       <c r="F113" s="67"/>
       <c r="G113" s="67"/>
       <c r="H113" s="68" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I113" s="68" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J113" s="67"/>
       <c r="K113" s="67"/>
@@ -14047,10 +14047,10 @@
       <c r="F114" s="67"/>
       <c r="G114" s="67"/>
       <c r="H114" s="68" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I114" s="68" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J114" s="67"/>
       <c r="K114" s="67"/>
@@ -14064,10 +14064,10 @@
       <c r="F115" s="67"/>
       <c r="G115" s="67"/>
       <c r="H115" s="68" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I115" s="68" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J115" s="67"/>
       <c r="K115" s="67"/>
@@ -14081,10 +14081,10 @@
       <c r="F116" s="67"/>
       <c r="G116" s="67"/>
       <c r="H116" s="68" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I116" s="68" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J116" s="67"/>
       <c r="K116" s="67"/>
@@ -14098,10 +14098,10 @@
       <c r="F117" s="67"/>
       <c r="G117" s="67"/>
       <c r="H117" s="68" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I117" s="68" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J117" s="67"/>
       <c r="K117" s="67"/>
@@ -14115,10 +14115,10 @@
       <c r="F118" s="67"/>
       <c r="G118" s="67"/>
       <c r="H118" s="68" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I118" s="68" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J118" s="67"/>
       <c r="K118" s="67"/>
@@ -14132,10 +14132,10 @@
       <c r="F119" s="67"/>
       <c r="G119" s="67"/>
       <c r="H119" s="68" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I119" s="68" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J119" s="67"/>
       <c r="K119" s="67"/>
@@ -14174,7 +14174,7 @@
       <c r="J124" s="74"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="s9Ci2VzJH+lZ+r08cGeqmIapFk6ZHOOcOf7qCQPvdUeHRRLkh9GAflBQHTVZv4//qek8JBmtZjy0zm1fsV2Lpw==" saltValue="nyvkWJ8TvmZtXlln8547DA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dy3m27mzZEN+SGEFmd/uusRbsxGmH34mdgShuubZsXNvb9zkVDtY5cXqT6ZB6l+bvpZIhIPYiCwOPD52eqnllg==" saltValue="wxaM7OG96zCsOUDsNdS7ag==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="14">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="K2:M2"/>
